--- a/docs/한재웅/요구사항정의서_v8.xlsx
+++ b/docs/한재웅/요구사항정의서_v8.xlsx
@@ -1,22 +1,258 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
+  <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\project\SKN27-FINAL-4Team\docs\한재웅\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <x:bookViews>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22836" windowHeight="8712" tabRatio="500"/>
+  </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" r:id="R41768ca81b8c4c07"/>
+    <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
   </x:sheets>
+  <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+  <x:si>
+    <x:t>시스템은 마이페이지 메인화면의 리포트 보관함 아티팩트 또는 버튼을 통해 마음리포트 보관함 페이지로 이동할 수 있도록 해야 한다. 보관함 진입 후의 주간·월간 캘린더, 일별 대표 감정 이모지, 리포트 상세 조회, 발급 기준 및 공유 기능은 마음리포트 모듈의 정책을 따른다. 마이페이지는 진입 동선, 빈 상태 안내, 리포트 생성 유도 문구, 목록 조회 실패 시 오류 메시지와 재시도 기능을 제공해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항 정의서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소분류(기능설명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 사용자의 대화기록에서 반복적으로 나타나는 관심 주제, 선호 표현, 감정 반응, 콘텐츠 취향을 분석해야 한다. 분석 결과는 '최근 관심사', '선호 경향', '변화 추이'로 구분해 제공하며, 데이터가 부족하거나 분석 기준을 충족하지 못한 경우에는 분석 불가 사유와 다음 갱신 가능 조건을 안내해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정 탈퇴·데이터 삭제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정적 방 일러스트 기반 메인 메뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자가 설정 페이지의 값을 변경하면 페이지 새로고침 없이 즉시 화면과 관련 공통 UI에 반영되어야 한다. 시스템은 변경 성공 시 확인 토스트를 표시하고, 저장 실패·네트워크 오류·권한 오류 발생 시 원인과 재시도 방법을 안내해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자는 언어, 테마, 접근성, 화면 표시 방식 등 설정 페이지에서 관리하는 개인 설정값을 기본값으로 초기화할 수 있어야 한다. 초기화 전 변경 대상과 복구 가능 여부를 안내하고, 초기화 완료 후 즉시 현재 화면에 반영해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 마이페이지 진입 시 정적 아이소메트릭 방 일러스트를 웹 화면의 메인 메뉴 배경으로 표시해야 한다. 방 내부의 프로필, 리포트 보관함, 개인 분석(MBTI 성향 분석, 취향 및 선호 경향 분석), 설정 등 주요 아티팩트는 이미지 위에 클릭 가능한 버튼 또는 링크 영역으로 배치해야 한다. 사용자가 마우스 클릭, 키보드 선택, 포커스 이동으로 아티팩트를 선택하면 호버·포커스·선택 피드백을 제공한 뒤 해당 페이지로 이동해야 하며, 작은 화면에서는 동일 기능을 목록 또는 그리드 메뉴로 함께 제공해야 한다. 로딩 실패 시에는 오류 메시지와 재시도 안내를 표시해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자는 현재 로그인된 브라우저 세션과 최근 접속 이력을 확인하고, 더 이상 사용하지 않는 세션을 종료할 수 있어야 한다. 세션 종료 시 해당 브라우저에서는 재로그인 전까지 서비스 접근이 제한되며, 현재 사용 중인 세션 종료 여부는 별도 확인 절차를 거쳐야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 사용자의 일반 자유형 대화기록을 분석 파이프라인을 통해 분석하여 대화에서 드러나는 최근의 MBTI 유사 성향과 변화 경향을 추정해야 한다. 분석 결과는 자기이해를 돕는 참고 정보로 제공하며, 추정 근거 리포트와 MBTI 축별 추정 점수 방사형 그래프로 표현하여 한눈에 볼 수 있어야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자는 설정 화면에서 로그인 계정, 닉네임, 가입 방식, 가입일 등 계정의 기본 정보를 확인할 수 있어야 한다. 이 화면은 다른 기능의 입력값을 직접 수정하지 않고, 상세 수정이 필요한 경우 해당 기능 화면으로 이동할 수 있는 안내만 제공해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자는 설정 화면에서 글자 크기, 애니메이션 최소화, 고대비 표시 등 화면 접근성 옵션을 변경할 수 있어야 한다. 변경된 옵션은 설정 페이지와 공통 UI 컴포넌트에 적용되며, 사용자가 언제든 기본값으로 되돌릴 수 있어야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자는 인터페이스 언어를 한국어 또는 영어로 선택할 수 있고, 화면 테마를 다크 모드 또는 라이트 모드로 변경할 수 있어야 한다. 변경된 언어와 테마는 로그인 계정 기준으로 저장되어 동일 브라우저 재방문 또는 다른 브라우저 로그인 후에도 유지되어야 하며, 접근성 기준을 고려해 텍스트 대비와 주요 버튼 가독성을 보장해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화기록 기반 취향 및 선호 경향 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화기록 기반 MBTI 성향 추정 및 경향 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비기능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자가 계정 탈퇴를 요청하면 시스템은 탈퇴 전 삭제 대상 데이터 범위와 복구 불가 여부를 안내해야 한다. 최종 확인 후 대화기록, 결과카드, 메모리, 개인화 설정, 웹 설정값 등 계정에 연결된 데이터를 삭제 처리하고, 삭제 완료 화면 및 필요 시 이메일 확인 안내를 제공해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리포트 보관함 연결</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비의료 참고 정보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정 내 계정 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SET-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정 기본 정보 조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정 자체 제공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 접근성 설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SET-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SET-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SET-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어·테마 설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전역 UI 설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로그인 세션 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정 데이터 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인정보보호 정책</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SET-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SET-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웹 계정 보안 설정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NF-SET-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정 즉시 반영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>추가설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필 조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정책·제약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마이페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인화면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정 페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설정값 초기화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UX 일관성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>온보딩 사용자 정보 연계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정적 이미지+클릭 영역 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인 분석 화면 자체 처리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음리포트 담당 범위와 연결</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 사용자가 온보딩에서 입력한 이름, 캐릭터, MBTI, 성별, 나이, 현재 나의 상태, 나를 표현하는 키워드, 관심 분야, 취미 등 기본 프로필 정보를 항목별로 조회할 수 있도록 해야 한다. 수정 가능한 항목은 온보딩 입력 항목과 충돌하지 않도록 동일한 데이터 기준을 사용하며, 수정 완료 시 변경된 정보가 마이페이지 표시와 대화 개인화 설정에 즉시 반영되어야 한다.</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+<x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="6">
     <x:font>
+      <x:name val="Carlito"/>
       <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">
@@ -29,10 +265,18 @@
   </x:fills>
   <x:borders count="9">
     <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
@@ -41,17 +285,23 @@
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
-      <x:top/>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
       <x:bottom style="dotted">
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
-      <x:left/>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
-      <x:top/>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
       <x:bottom style="dotted">
         <x:color auto="1"/>
       </x:bottom>
@@ -66,7 +316,9 @@
       <x:top style="dotted">
         <x:color auto="1"/>
       </x:top>
-      <x:bottom/>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
@@ -89,14 +341,20 @@
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
-      <x:top/>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
-      <x:left/>
-      <x:right/>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
       <x:top style="thin">
         <x:color auto="1"/>
       </x:top>
@@ -105,7 +363,9 @@
       </x:bottom>
     </x:border>
     <x:border>
-      <x:left/>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
@@ -123,11 +383,18 @@
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
-      <x:top/>
-      <x:bottom/>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="3">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -135,102 +402,361 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="top"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="2">
-    <x:cellStyle name="표준" xfId="0"/>
-    <x:cellStyle name="Normal" xfId="1"/>
+  <x:cellStyles count="3">
+    <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
+    <x:cellStyle name="Normal" xfId="2"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:dxf/>
     <x:dxf>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
           <x:bgColor rgb="ffaebfea"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:dxf>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
           <x:bgColor rgb="ff94a5df"/>
         </x:patternFill>
       </x:fill>
@@ -245,17 +771,124 @@
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
           <x:bgColor rgb="ff6182d6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="Normal Style 1 - Accent 1" defaultPivotStyle="Light Style 1 - Accent 1">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
 </x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -381,17 +1014,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="13.199999809265137"/>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet1"/>
+  <x:dimension ref="A1:Z225"/>
+  <x:sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="14.199999999999999"/>
   <x:cols>
     <x:col min="5" max="5" width="56.63671875" style="16" customWidth="1"/>
     <x:col min="6" max="6" width="56" style="7" customWidth="1"/>
     <x:col min="7" max="7" width="26.76953125" style="16" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="18" customHeight="1">
-      <x:c r="A1" s="21" t="str">
-        <x:v>요구사항 정의서</x:v>
+    <x:row r="1" spans="1:26" ht="18" customHeight="1">
+      <x:c r="A1" s="21" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -419,7 +1054,7 @@
       <x:c r="Y1" s="1"/>
       <x:c r="Z1" s="1"/>
     </x:row>
-    <x:row r="2" ht="18" customHeight="1">
+    <x:row r="2" spans="1:26" ht="18" customHeight="1">
       <x:c r="A2" s="1"/>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -447,21 +1082,21 @@
       <x:c r="Y2" s="1"/>
       <x:c r="Z2" s="1"/>
     </x:row>
-    <x:row r="3" ht="36" customHeight="1">
-      <x:c r="A3" s="24" t="str">
-        <x:v>분류</x:v>
+    <x:row r="3" spans="1:26" ht="36" customHeight="1">
+      <x:c r="A3" s="20" t="s">
+        <x:v>16</x:v>
       </x:c>
-      <x:c r="B3" s="24" t="str">
-        <x:v>요구사항명</x:v>
+      <x:c r="B3" s="20" t="s">
+        <x:v>52</x:v>
       </x:c>
-      <x:c r="C3" s="24"/>
-      <x:c r="D3" s="24"/>
-      <x:c r="E3" s="24"/>
-      <x:c r="F3" s="24" t="str">
-        <x:v>추가설명</x:v>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20" t="s">
+        <x:v>50</x:v>
       </x:c>
-      <x:c r="G3" s="24" t="str">
-        <x:v>비고</x:v>
+      <x:c r="G3" s="20" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
       <x:c r="I3" s="1"/>
@@ -483,22 +1118,22 @@
       <x:c r="Y3" s="1"/>
       <x:c r="Z3" s="1"/>
     </x:row>
-    <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="24"/>
-      <x:c r="B4" s="14" t="str">
-        <x:v>대분류</x:v>
+    <x:row r="4" spans="1:26" ht="18" customHeight="1">
+      <x:c r="A4" s="20"/>
+      <x:c r="B4" s="14" t="s">
+        <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>중분류</x:v>
+      <x:c r="C4" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>요구사항 ID</x:v>
+      <x:c r="D4" s="14" t="s">
+        <x:v>58</x:v>
       </x:c>
-      <x:c r="E4" s="6" t="str">
-        <x:v>소분류(기능설명)</x:v>
+      <x:c r="E4" s="6" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="24"/>
-      <x:c r="G4" s="24"/>
+      <x:c r="F4" s="20"/>
+      <x:c r="G4" s="20"/>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
       <x:c r="J4" s="1"/>
@@ -519,27 +1154,27 @@
       <x:c r="Y4" s="1"/>
       <x:c r="Z4" s="1"/>
     </x:row>
-    <x:row r="5" ht="96" customHeight="1">
-      <x:c r="A5" s="19" t="str">
-        <x:v>기능</x:v>
+    <x:row r="5" spans="1:26" ht="96" customHeight="1">
+      <x:c r="A5" s="19" t="s">
+        <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="19" t="str">
-        <x:v>마이페이지</x:v>
+      <x:c r="B5" s="19" t="s">
+        <x:v>55</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="str">
-        <x:v>메인화면</x:v>
+      <x:c r="C5" s="15" t="s">
+        <x:v>56</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>F-MY-001</x:v>
+      <x:c r="D5" s="14" t="s">
+        <x:v>26</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>정적 방 일러스트 기반 메인 메뉴</x:v>
+      <x:c r="E5" s="14" t="s">
+        <x:v>5</x:v>
       </x:c>
-      <x:c r="F5" s="17" t="str">
-        <x:v>시스템은 마이페이지 진입 시 정적 아이소메트릭 방 일러스트를 웹 화면의 메인 메뉴 배경으로 표시해야 한다. 방 내부의 프로필, 리포트 보관함, 개인 분석(MBTI 성향 분석, 취향 및 선호 경향 분석), 설정 등 주요 아티팩트는 이미지 위에 클릭 가능한 버튼 또는 링크 영역으로 배치해야 한다. 사용자가 마우스 클릭, 키보드 선택, 포커스 이동으로 아티팩트를 선택하면 호버·포커스·선택 피드백을 제공한 뒤 해당 페이지로 이동해야 하며, 작은 화면에서는 동일 기능을 목록 또는 그리드 메뉴로 함께 제공해야 한다. 로딩 실패 시에는 오류 메시지와 재시도 안내를 표시해야 한다.</x:v>
+      <x:c r="F5" s="17" t="s">
+        <x:v>8</x:v>
       </x:c>
-      <x:c r="G5" s="8" t="str">
-        <x:v>정적 이미지+클릭 영역 방식</x:v>
+      <x:c r="G5" s="8" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
       <x:c r="I5" s="1"/>
@@ -561,23 +1196,23 @@
       <x:c r="Y5" s="1"/>
       <x:c r="Z5" s="1"/>
     </x:row>
-    <x:row r="6" ht="72" customHeight="1">
+    <x:row r="6" spans="1:26" ht="72" customHeight="1">
       <x:c r="A6" s="19"/>
       <x:c r="B6" s="19"/>
-      <x:c r="C6" s="22" t="str">
-        <x:v>조회</x:v>
+      <x:c r="C6" s="22" t="s">
+        <x:v>18</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>F-MY-002</x:v>
+      <x:c r="D6" s="14" t="s">
+        <x:v>25</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>프로필 조회</x:v>
+      <x:c r="E6" s="14" t="s">
+        <x:v>51</x:v>
       </x:c>
-      <x:c r="F6" s="17" t="str">
-        <x:v>시스템은 사용자가 온보딩에서 입력한 이름, 캐릭터, MBTI, 성별, 나이, 현재 나의 상태, 나를 표현하는 키워드, 관심 분야, 취미 등 기본 프로필 정보를 항목별로 조회할 수 있도록 해야 한다. 수정 가능한 항목은 온보딩 입력 항목과 충돌하지 않도록 동일한 데이터 기준을 사용하며, 수정 완료 시 변경된 정보가 마이페이지 표시와 대화 개인화 설정에 즉시 반영되어야 한다.</x:v>
+      <x:c r="F6" s="17" t="s">
+        <x:v>65</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="str">
-        <x:v>온보딩 사용자 정보 연계</x:v>
+      <x:c r="G6" s="8" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
       <x:c r="I6" s="1"/>
@@ -599,21 +1234,21 @@
       <x:c r="Y6" s="1"/>
       <x:c r="Z6" s="1"/>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
+    <x:row r="7" spans="1:26" ht="72" customHeight="1">
       <x:c r="A7" s="19"/>
       <x:c r="B7" s="19"/>
       <x:c r="C7" s="23"/>
-      <x:c r="D7" s="14" t="str">
-        <x:v>F-MY-003</x:v>
+      <x:c r="D7" s="14" t="s">
+        <x:v>28</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>리포트 보관함 연결</x:v>
+      <x:c r="E7" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="str">
-        <x:v>시스템은 마이페이지 메인화면의 리포트 보관함 아티팩트 또는 버튼을 통해 마음리포트 보관함 페이지로 이동할 수 있도록 해야 한다. 보관함 진입 후의 주간·월간 캘린더, 일별 대표 감정 이모지, 리포트 상세 조회, 발급 기준 및 공유 기능은 마음리포트 모듈의 정책을 따른다. 마이페이지는 진입 동선, 빈 상태 안내, 리포트 생성 유도 문구, 목록 조회 실패 시 오류 메시지와 재시도 기능을 제공해야 한다.</x:v>
+      <x:c r="F7" s="17" t="s">
+        <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="str">
-        <x:v>마음리포트 담당 범위와 연결</x:v>
+      <x:c r="G7" s="8" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H7" s="1"/>
       <x:c r="I7" s="1"/>
@@ -635,23 +1270,23 @@
       <x:c r="Y7" s="1"/>
       <x:c r="Z7" s="1"/>
     </x:row>
-    <x:row r="8" ht="60" customHeight="1">
+    <x:row r="8" spans="1:26" ht="60" customHeight="1">
       <x:c r="A8" s="19"/>
       <x:c r="B8" s="19"/>
-      <x:c r="C8" s="22" t="str">
-        <x:v>개인 분석</x:v>
+      <x:c r="C8" s="22" t="s">
+        <x:v>54</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>F-MY-004</x:v>
+      <x:c r="D8" s="14" t="s">
+        <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>대화기록 기반 MBTI 성향 추정 및 경향 분석</x:v>
+      <x:c r="E8" s="14" t="s">
+        <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="17" t="str">
-        <x:v>시스템은 사용자의 일반 자유형 대화기록을 분석 파이프라인을 통해 분석하여 대화에서 드러나는 최근의 MBTI 유사 성향과 변화 경향을 추정해야 한다. 분석 결과는 자기이해를 돕는 참고 정보로 제공하며, 추정 근거 리포트와 MBTI 축별 추정 점수 방사형 그래프로 표현하여 한눈에 볼 수 있어야 한다.</x:v>
+      <x:c r="F8" s="17" t="s">
+        <x:v>10</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="str">
-        <x:v>비의료 참고 정보</x:v>
+      <x:c r="G8" s="8" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H8" s="1"/>
       <x:c r="I8" s="1"/>
@@ -673,21 +1308,21 @@
       <x:c r="Y8" s="1"/>
       <x:c r="Z8" s="1"/>
     </x:row>
-    <x:row r="9" ht="72" customHeight="1">
+    <x:row r="9" spans="1:26" ht="72" customHeight="1">
       <x:c r="A9" s="19"/>
       <x:c r="B9" s="19"/>
       <x:c r="C9" s="23"/>
-      <x:c r="D9" s="14" t="str">
-        <x:v>F-MY-005</x:v>
+      <x:c r="D9" s="14" t="s">
+        <x:v>32</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>대화기록 기반 취향 및 선호 경향 분석</x:v>
+      <x:c r="E9" s="14" t="s">
+        <x:v>14</x:v>
       </x:c>
-      <x:c r="F9" s="17" t="str">
-        <x:v>시스템은 사용자의 대화기록에서 반복적으로 나타나는 관심 주제, 선호 표현, 감정 반응, 콘텐츠 취향을 분석해야 한다. 분석 결과는 '최근 관심사', '선호 경향', '변화 추이'로 구분해 제공하며, 데이터가 부족하거나 분석 기준을 충족하지 못한 경우에는 분석 불가 사유와 다음 갱신 가능 조건을 안내해야 한다.</x:v>
+      <x:c r="F9" s="17" t="s">
+        <x:v>3</x:v>
       </x:c>
-      <x:c r="G9" s="8" t="str">
-        <x:v>개인 분석 화면 자체 처리</x:v>
+      <x:c r="G9" s="8" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H9" s="1"/>
       <x:c r="I9" s="1"/>
@@ -709,25 +1344,25 @@
       <x:c r="Y9" s="1"/>
       <x:c r="Z9" s="1"/>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
+    <x:row r="10" spans="1:26" ht="72" customHeight="1">
       <x:c r="A10" s="19"/>
-      <x:c r="B10" s="20" t="str">
-        <x:v>설정 페이지</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>57</x:v>
       </x:c>
-      <x:c r="C10" s="22" t="str">
-        <x:v>설정</x:v>
+      <x:c r="C10" s="22" t="s">
+        <x:v>22</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="str">
-        <x:v>F-SET-001</x:v>
+      <x:c r="D10" s="14" t="s">
+        <x:v>33</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="str">
-        <x:v>계정 기본 정보 조회</x:v>
+      <x:c r="E10" s="14" t="s">
+        <x:v>34</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="str">
-        <x:v>사용자는 설정 화면에서 로그인 계정, 닉네임, 가입 방식, 가입일 등 계정의 기본 정보를 확인할 수 있어야 한다. 이 화면은 다른 기능의 입력값을 직접 수정하지 않고, 상세 수정이 필요한 경우 해당 기능 화면으로 이동할 수 있는 안내만 제공해야 한다.</x:v>
+      <x:c r="F10" s="17" t="s">
+        <x:v>11</x:v>
       </x:c>
-      <x:c r="G10" s="8" t="str">
-        <x:v>설정 내 계정 확인</x:v>
+      <x:c r="G10" s="8" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H10" s="1"/>
       <x:c r="I10" s="1"/>
@@ -749,21 +1384,21 @@
       <x:c r="Y10" s="1"/>
       <x:c r="Z10" s="1"/>
     </x:row>
-    <x:row r="11" ht="60" customHeight="1">
+    <x:row r="11" spans="1:26" ht="60" customHeight="1">
       <x:c r="A11" s="19"/>
       <x:c r="B11" s="20"/>
       <x:c r="C11" s="23"/>
-      <x:c r="D11" s="14" t="str">
-        <x:v>F-SET-002</x:v>
+      <x:c r="D11" s="14" t="s">
+        <x:v>39</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="str">
-        <x:v>언어·테마 설정</x:v>
+      <x:c r="E11" s="14" t="s">
+        <x:v>40</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="str">
-        <x:v>사용자는 인터페이스 언어를 한국어 또는 영어로 선택할 수 있고, 화면 테마를 다크 모드 또는 라이트 모드로 변경할 수 있어야 한다. 변경된 언어와 테마는 로그인 계정 기준으로 저장되어 동일 브라우저 재방문 또는 다른 브라우저 로그인 후에도 유지되어야 하며, 접근성 기준을 고려해 텍스트 대비와 주요 버튼 가독성을 보장해야 한다.</x:v>
+      <x:c r="F11" s="17" t="s">
+        <x:v>13</x:v>
       </x:c>
-      <x:c r="G11" s="8" t="str">
-        <x:v>전역 UI 설정</x:v>
+      <x:c r="G11" s="8" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H11" s="1"/>
       <x:c r="I11" s="1"/>
@@ -785,96 +1420,96 @@
       <x:c r="Y11" s="1"/>
       <x:c r="Z11" s="1"/>
     </x:row>
-    <x:row r="12" ht="72" customHeight="1">
+    <x:row r="12" spans="1:7" ht="72" customHeight="1">
       <x:c r="A12" s="19"/>
       <x:c r="B12" s="20"/>
       <x:c r="C12" s="18"/>
-      <x:c r="D12" s="14" t="str">
-        <x:v>F-SET-003</x:v>
+      <x:c r="D12" s="14" t="s">
+        <x:v>37</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="str">
-        <x:v>화면 접근성 설정</x:v>
+      <x:c r="E12" s="14" t="s">
+        <x:v>36</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="str">
-        <x:v>사용자는 설정 화면에서 글자 크기, 애니메이션 최소화, 고대비 표시 등 화면 접근성 옵션을 변경할 수 있어야 한다. 변경된 옵션은 설정 페이지와 공통 UI 컴포넌트에 적용되며, 사용자가 언제든 기본값으로 되돌릴 수 있어야 한다.</x:v>
+      <x:c r="F12" s="17" t="s">
+        <x:v>12</x:v>
       </x:c>
-      <x:c r="G12" s="8" t="str">
-        <x:v>설정 자체 제공</x:v>
+      <x:c r="G12" s="8" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="60" customHeight="1">
+    <x:row r="13" spans="1:7" ht="60" customHeight="1">
       <x:c r="A13" s="19"/>
       <x:c r="B13" s="20"/>
-      <x:c r="C13" s="25"/>
-      <x:c r="D13" s="14" t="str">
-        <x:v>F-SET-004</x:v>
+      <x:c r="C13" s="24"/>
+      <x:c r="D13" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="str">
-        <x:v>로그인 세션 관리</x:v>
+      <x:c r="E13" s="14" t="s">
+        <x:v>42</x:v>
       </x:c>
-      <x:c r="F13" s="17" t="str">
-        <x:v>사용자는 현재 로그인된 브라우저 세션과 최근 접속 이력을 확인하고, 더 이상 사용하지 않는 세션을 종료할 수 있어야 한다. 세션 종료 시 해당 브라우저에서는 재로그인 전까지 서비스 접근이 제한되며, 현재 사용 중인 세션 종료 여부는 별도 확인 절차를 거쳐야 한다.</x:v>
+      <x:c r="F13" s="17" t="s">
+        <x:v>9</x:v>
       </x:c>
-      <x:c r="G13" s="8" t="str">
-        <x:v>웹 계정 보안 설정</x:v>
+      <x:c r="G13" s="8" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="72" customHeight="1">
+    <x:row r="14" spans="1:7" ht="72" customHeight="1">
       <x:c r="A14" s="19"/>
       <x:c r="B14" s="20"/>
       <x:c r="C14" s="23"/>
-      <x:c r="D14" s="14" t="str">
-        <x:v>F-SET-005</x:v>
+      <x:c r="D14" s="14" t="s">
+        <x:v>46</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="str">
-        <x:v>설정값 초기화</x:v>
+      <x:c r="E14" s="14" t="s">
+        <x:v>59</x:v>
       </x:c>
-      <x:c r="F14" s="17" t="str">
-        <x:v>사용자는 언어, 테마, 접근성, 화면 표시 방식 등 설정 페이지에서 관리하는 개인 설정값을 기본값으로 초기화할 수 있어야 한다. 초기화 전 변경 대상과 복구 가능 여부를 안내하고, 초기화 완료 후 즉시 현재 화면에 반영해야 한다.</x:v>
+      <x:c r="F14" s="17" t="s">
+        <x:v>7</x:v>
       </x:c>
-      <x:c r="G14" s="8" t="str">
-        <x:v>설정 데이터 관리</x:v>
+      <x:c r="G14" s="8" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="60" customHeight="1">
+    <x:row r="15" spans="1:7" ht="60" customHeight="1">
       <x:c r="A15" s="19"/>
       <x:c r="B15" s="20"/>
       <x:c r="C15" s="23"/>
-      <x:c r="D15" s="14" t="str">
-        <x:v>F-SET-006</x:v>
+      <x:c r="D15" s="14" t="s">
+        <x:v>45</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="str">
-        <x:v>계정 탈퇴·데이터 삭제</x:v>
+      <x:c r="E15" s="14" t="s">
+        <x:v>4</x:v>
       </x:c>
-      <x:c r="F15" s="17" t="str">
-        <x:v>사용자가 계정 탈퇴를 요청하면 시스템은 탈퇴 전 삭제 대상 데이터 범위와 복구 불가 여부를 안내해야 한다. 최종 확인 후 대화기록, 결과카드, 메모리, 개인화 설정, 웹 설정값 등 계정에 연결된 데이터를 삭제 처리하고, 삭제 완료 화면 및 필요 시 이메일 확인 안내를 제공해야 한다.</x:v>
+      <x:c r="F15" s="17" t="s">
+        <x:v>24</x:v>
       </x:c>
-      <x:c r="G15" s="8" t="str">
-        <x:v>개인정보보호 정책</x:v>
+      <x:c r="G15" s="8" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="60" customHeight="1">
-      <x:c r="A16" s="19" t="str">
-        <x:v>비기능</x:v>
+    <x:row r="16" spans="1:7" ht="60" customHeight="1">
+      <x:c r="A16" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="20"/>
-      <x:c r="C16" s="23" t="str">
-        <x:v>정책·제약</x:v>
+      <x:c r="C16" s="23" t="s">
+        <x:v>53</x:v>
       </x:c>
-      <x:c r="D16" s="14" t="str">
-        <x:v>NF-SET-001</x:v>
+      <x:c r="D16" s="14" t="s">
+        <x:v>48</x:v>
       </x:c>
-      <x:c r="E16" s="14" t="str">
-        <x:v>설정 즉시 반영</x:v>
+      <x:c r="E16" s="14" t="s">
+        <x:v>49</x:v>
       </x:c>
-      <x:c r="F16" s="17" t="str">
-        <x:v>사용자가 설정 페이지의 값을 변경하면 페이지 새로고침 없이 즉시 화면과 관련 공통 UI에 반영되어야 한다. 시스템은 변경 성공 시 확인 토스트를 표시하고, 저장 실패·네트워크 오류·권한 오류 발생 시 원인과 재시도 방법을 안내해야 한다.</x:v>
+      <x:c r="F16" s="17" t="s">
+        <x:v>6</x:v>
       </x:c>
-      <x:c r="G16" s="8" t="str">
-        <x:v>UX 일관성</x:v>
+      <x:c r="G16" s="8" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="60" customHeight="1">
+    <x:row r="17" spans="1:7" ht="60" customHeight="1">
       <x:c r="A17" s="19"/>
       <x:c r="B17" s="20"/>
       <x:c r="C17" s="23"/>
@@ -883,7 +1518,7 @@
       <x:c r="F17" s="17"/>
       <x:c r="G17" s="8"/>
     </x:row>
-    <x:row r="18" ht="60" customHeight="1">
+    <x:row r="18" spans="1:7" ht="60" customHeight="1">
       <x:c r="A18" s="19"/>
       <x:c r="B18" s="20"/>
       <x:c r="C18" s="23"/>
@@ -892,7 +1527,7 @@
       <x:c r="F18" s="17"/>
       <x:c r="G18" s="8"/>
     </x:row>
-    <x:row r="19" ht="60" customHeight="1">
+    <x:row r="19" spans="1:7" ht="60" customHeight="1">
       <x:c r="A19" s="19"/>
       <x:c r="B19" s="20"/>
       <x:c r="C19" s="23"/>
@@ -901,7 +1536,7 @@
       <x:c r="F19" s="17"/>
       <x:c r="G19" s="8"/>
     </x:row>
-    <x:row r="20" ht="60" customHeight="1">
+    <x:row r="20" spans="1:7" ht="60" customHeight="1">
       <x:c r="A20" s="14"/>
       <x:c r="B20" s="20"/>
       <x:c r="C20" s="14"/>
@@ -910,7 +1545,7 @@
       <x:c r="F20" s="9"/>
       <x:c r="G20" s="10"/>
     </x:row>
-    <x:row r="21" ht="60" customHeight="1">
+    <x:row r="21" spans="1:7" ht="60" customHeight="1">
       <x:c r="A21" s="20"/>
       <x:c r="B21" s="20"/>
       <x:c r="C21" s="20"/>
@@ -919,7 +1554,7 @@
       <x:c r="F21" s="13"/>
       <x:c r="G21" s="12"/>
     </x:row>
-    <x:row r="22" ht="60" customHeight="1">
+    <x:row r="22" spans="1:7" ht="60" customHeight="1">
       <x:c r="A22" s="20"/>
       <x:c r="B22" s="20"/>
       <x:c r="C22" s="20"/>
@@ -928,7 +1563,7 @@
       <x:c r="F22" s="13"/>
       <x:c r="G22" s="12"/>
     </x:row>
-    <x:row r="23" ht="60" customHeight="1">
+    <x:row r="23" spans="1:7" ht="60" customHeight="1">
       <x:c r="A23" s="20"/>
       <x:c r="B23" s="20"/>
       <x:c r="C23" s="20"/>
@@ -937,7 +1572,7 @@
       <x:c r="F23" s="13"/>
       <x:c r="G23" s="12"/>
     </x:row>
-    <x:row r="24" ht="60" customHeight="1">
+    <x:row r="24" spans="1:7" ht="60" customHeight="1">
       <x:c r="A24" s="20"/>
       <x:c r="B24" s="20"/>
       <x:c r="C24" s="20"/>
@@ -946,7 +1581,7 @@
       <x:c r="F24" s="13"/>
       <x:c r="G24" s="12"/>
     </x:row>
-    <x:row r="25" ht="60" customHeight="1">
+    <x:row r="25" spans="1:7" ht="60" customHeight="1">
       <x:c r="A25" s="20"/>
       <x:c r="B25" s="20"/>
       <x:c r="C25" s="14"/>
@@ -955,7 +1590,7 @@
       <x:c r="F25" s="13"/>
       <x:c r="G25" s="12"/>
     </x:row>
-    <x:row r="26" ht="60" customHeight="1">
+    <x:row r="26" spans="1:7" ht="60" customHeight="1">
       <x:c r="A26" s="20"/>
       <x:c r="B26" s="20"/>
       <x:c r="C26" s="20"/>
@@ -964,7 +1599,7 @@
       <x:c r="F26" s="13"/>
       <x:c r="G26" s="12"/>
     </x:row>
-    <x:row r="27" ht="60" customHeight="1">
+    <x:row r="27" spans="1:7" ht="60" customHeight="1">
       <x:c r="A27" s="20"/>
       <x:c r="B27" s="20"/>
       <x:c r="C27" s="20"/>
@@ -973,7 +1608,7 @@
       <x:c r="F27" s="13"/>
       <x:c r="G27" s="12"/>
     </x:row>
-    <x:row r="28" ht="60" customHeight="1">
+    <x:row r="28" spans="1:26" ht="60" customHeight="1">
       <x:c r="A28" s="20"/>
       <x:c r="B28" s="20"/>
       <x:c r="C28" s="14"/>
@@ -1001,7 +1636,7 @@
       <x:c r="Y28" s="1"/>
       <x:c r="Z28" s="1"/>
     </x:row>
-    <x:row r="29" ht="18" customHeight="1">
+    <x:row r="29" spans="1:26" ht="18" customHeight="1">
       <x:c r="A29" s="3"/>
       <x:c r="B29" s="3"/>
       <x:c r="C29" s="2"/>
@@ -1029,7 +1664,7 @@
       <x:c r="Y29" s="1"/>
       <x:c r="Z29" s="1"/>
     </x:row>
-    <x:row r="30" ht="18" customHeight="1">
+    <x:row r="30" spans="1:26" ht="18" customHeight="1">
       <x:c r="A30" s="3"/>
       <x:c r="B30" s="3"/>
       <x:c r="C30" s="3"/>
@@ -1057,7 +1692,7 @@
       <x:c r="Y30" s="1"/>
       <x:c r="Z30" s="1"/>
     </x:row>
-    <x:row r="31" ht="18" customHeight="1">
+    <x:row r="31" spans="1:26" ht="18" customHeight="1">
       <x:c r="A31" s="3"/>
       <x:c r="B31" s="3"/>
       <x:c r="C31" s="3"/>
@@ -1085,7 +1720,7 @@
       <x:c r="Y31" s="1"/>
       <x:c r="Z31" s="1"/>
     </x:row>
-    <x:row r="32" ht="18" customHeight="1">
+    <x:row r="32" spans="1:26" ht="18" customHeight="1">
       <x:c r="A32" s="3"/>
       <x:c r="B32" s="3"/>
       <x:c r="C32" s="2"/>
@@ -1113,7 +1748,7 @@
       <x:c r="Y32" s="1"/>
       <x:c r="Z32" s="1"/>
     </x:row>
-    <x:row r="33" ht="18" customHeight="1">
+    <x:row r="33" spans="1:26" ht="18" customHeight="1">
       <x:c r="A33" s="3"/>
       <x:c r="B33" s="3"/>
       <x:c r="C33" s="3"/>
@@ -1141,7 +1776,7 @@
       <x:c r="Y33" s="1"/>
       <x:c r="Z33" s="1"/>
     </x:row>
-    <x:row r="34" ht="18" customHeight="1">
+    <x:row r="34" spans="1:26" ht="18" customHeight="1">
       <x:c r="A34" s="2"/>
       <x:c r="B34" s="2"/>
       <x:c r="C34" s="2"/>
@@ -1169,7 +1804,7 @@
       <x:c r="Y34" s="1"/>
       <x:c r="Z34" s="1"/>
     </x:row>
-    <x:row r="35" ht="18" customHeight="1">
+    <x:row r="35" spans="1:26" ht="18" customHeight="1">
       <x:c r="A35" s="3"/>
       <x:c r="B35" s="3"/>
       <x:c r="C35" s="3"/>
@@ -1197,7 +1832,7 @@
       <x:c r="Y35" s="1"/>
       <x:c r="Z35" s="1"/>
     </x:row>
-    <x:row r="36" ht="18" customHeight="1">
+    <x:row r="36" spans="1:26" ht="18" customHeight="1">
       <x:c r="A36" s="3"/>
       <x:c r="B36" s="3"/>
       <x:c r="C36" s="3"/>
@@ -1225,7 +1860,7 @@
       <x:c r="Y36" s="1"/>
       <x:c r="Z36" s="1"/>
     </x:row>
-    <x:row r="37" ht="18" customHeight="1">
+    <x:row r="37" spans="1:26" ht="18" customHeight="1">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
@@ -1253,7 +1888,7 @@
       <x:c r="Y37" s="1"/>
       <x:c r="Z37" s="1"/>
     </x:row>
-    <x:row r="38" ht="18" customHeight="1">
+    <x:row r="38" spans="1:26" ht="18" customHeight="1">
       <x:c r="A38" s="3"/>
       <x:c r="B38" s="3"/>
       <x:c r="C38" s="2"/>
@@ -1281,7 +1916,7 @@
       <x:c r="Y38" s="1"/>
       <x:c r="Z38" s="1"/>
     </x:row>
-    <x:row r="39" ht="18" customHeight="1">
+    <x:row r="39" spans="1:26" ht="18" customHeight="1">
       <x:c r="A39" s="3"/>
       <x:c r="B39" s="3"/>
       <x:c r="C39" s="3"/>
@@ -1309,7 +1944,7 @@
       <x:c r="Y39" s="1"/>
       <x:c r="Z39" s="1"/>
     </x:row>
-    <x:row r="40" ht="18" customHeight="1">
+    <x:row r="40" spans="1:26" ht="18" customHeight="1">
       <x:c r="A40" s="3"/>
       <x:c r="B40" s="3"/>
       <x:c r="C40" s="2"/>
@@ -1337,7 +1972,7 @@
       <x:c r="Y40" s="1"/>
       <x:c r="Z40" s="1"/>
     </x:row>
-    <x:row r="41" ht="18" customHeight="1">
+    <x:row r="41" spans="1:26" ht="18" customHeight="1">
       <x:c r="A41" s="3"/>
       <x:c r="B41" s="3"/>
       <x:c r="C41" s="3"/>
@@ -1365,7 +2000,7 @@
       <x:c r="Y41" s="1"/>
       <x:c r="Z41" s="1"/>
     </x:row>
-    <x:row r="42" ht="18" customHeight="1">
+    <x:row r="42" spans="1:26" ht="18" customHeight="1">
       <x:c r="A42" s="2"/>
       <x:c r="B42" s="2"/>
       <x:c r="C42" s="2"/>
@@ -1393,7 +2028,7 @@
       <x:c r="Y42" s="1"/>
       <x:c r="Z42" s="1"/>
     </x:row>
-    <x:row r="43" ht="18" customHeight="1">
+    <x:row r="43" spans="1:26" ht="18" customHeight="1">
       <x:c r="A43" s="3"/>
       <x:c r="B43" s="3"/>
       <x:c r="C43" s="3"/>
@@ -1421,7 +2056,7 @@
       <x:c r="Y43" s="1"/>
       <x:c r="Z43" s="1"/>
     </x:row>
-    <x:row r="44" ht="18" customHeight="1">
+    <x:row r="44" spans="1:26" ht="18" customHeight="1">
       <x:c r="A44" s="3"/>
       <x:c r="B44" s="3"/>
       <x:c r="C44" s="2"/>
@@ -1449,7 +2084,7 @@
       <x:c r="Y44" s="1"/>
       <x:c r="Z44" s="1"/>
     </x:row>
-    <x:row r="45" ht="18" customHeight="1">
+    <x:row r="45" spans="1:26" ht="18" customHeight="1">
       <x:c r="A45" s="3"/>
       <x:c r="B45" s="3"/>
       <x:c r="C45" s="3"/>
@@ -1477,7 +2112,7 @@
       <x:c r="Y45" s="1"/>
       <x:c r="Z45" s="1"/>
     </x:row>
-    <x:row r="46" ht="18" customHeight="1">
+    <x:row r="46" spans="1:26" ht="18" customHeight="1">
       <x:c r="A46" s="2"/>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -1505,7 +2140,7 @@
       <x:c r="Y46" s="1"/>
       <x:c r="Z46" s="1"/>
     </x:row>
-    <x:row r="47" ht="18" customHeight="1">
+    <x:row r="47" spans="1:26" ht="18" customHeight="1">
       <x:c r="A47" s="2"/>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -1533,7 +2168,7 @@
       <x:c r="Y47" s="1"/>
       <x:c r="Z47" s="1"/>
     </x:row>
-    <x:row r="48" ht="18" customHeight="1">
+    <x:row r="48" spans="1:26" ht="18" customHeight="1">
       <x:c r="A48" s="2"/>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -1561,7 +2196,7 @@
       <x:c r="Y48" s="1"/>
       <x:c r="Z48" s="1"/>
     </x:row>
-    <x:row r="49" ht="18" customHeight="1">
+    <x:row r="49" spans="1:26" ht="18" customHeight="1">
       <x:c r="A49" s="2"/>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -1589,7 +2224,7 @@
       <x:c r="Y49" s="1"/>
       <x:c r="Z49" s="1"/>
     </x:row>
-    <x:row r="50" ht="18" customHeight="1">
+    <x:row r="50" spans="1:26" ht="18" customHeight="1">
       <x:c r="A50" s="2"/>
       <x:c r="B50" s="2"/>
       <x:c r="C50" s="2"/>
@@ -1617,7 +2252,7 @@
       <x:c r="Y50" s="1"/>
       <x:c r="Z50" s="1"/>
     </x:row>
-    <x:row r="51" ht="18" customHeight="1">
+    <x:row r="51" spans="1:26" ht="18" customHeight="1">
       <x:c r="A51" s="2"/>
       <x:c r="B51" s="2"/>
       <x:c r="C51" s="2"/>
@@ -1645,7 +2280,7 @@
       <x:c r="Y51" s="1"/>
       <x:c r="Z51" s="1"/>
     </x:row>
-    <x:row r="52" ht="18" customHeight="1">
+    <x:row r="52" spans="1:26" ht="18" customHeight="1">
       <x:c r="A52" s="2"/>
       <x:c r="B52" s="2"/>
       <x:c r="C52" s="2"/>
@@ -1673,7 +2308,7 @@
       <x:c r="Y52" s="1"/>
       <x:c r="Z52" s="1"/>
     </x:row>
-    <x:row r="53" ht="18" customHeight="1">
+    <x:row r="53" spans="1:26" ht="18" customHeight="1">
       <x:c r="A53" s="2"/>
       <x:c r="B53" s="2"/>
       <x:c r="C53" s="2"/>
@@ -1701,7 +2336,7 @@
       <x:c r="Y53" s="1"/>
       <x:c r="Z53" s="1"/>
     </x:row>
-    <x:row r="54" ht="18" customHeight="1">
+    <x:row r="54" spans="1:26" ht="18" customHeight="1">
       <x:c r="A54" s="2"/>
       <x:c r="B54" s="2"/>
       <x:c r="C54" s="2"/>
@@ -1729,7 +2364,7 @@
       <x:c r="Y54" s="1"/>
       <x:c r="Z54" s="1"/>
     </x:row>
-    <x:row r="55" ht="18" customHeight="1">
+    <x:row r="55" spans="1:26" ht="18" customHeight="1">
       <x:c r="A55" s="2"/>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -1757,7 +2392,7 @@
       <x:c r="Y55" s="1"/>
       <x:c r="Z55" s="1"/>
     </x:row>
-    <x:row r="56" ht="18" customHeight="1">
+    <x:row r="56" spans="1:26" ht="18" customHeight="1">
       <x:c r="A56" s="2"/>
       <x:c r="B56" s="2"/>
       <x:c r="C56" s="2"/>
@@ -1785,7 +2420,7 @@
       <x:c r="Y56" s="1"/>
       <x:c r="Z56" s="1"/>
     </x:row>
-    <x:row r="57" ht="18" customHeight="1">
+    <x:row r="57" spans="1:26" ht="18" customHeight="1">
       <x:c r="A57" s="2"/>
       <x:c r="B57" s="2"/>
       <x:c r="C57" s="2"/>
@@ -1813,7 +2448,7 @@
       <x:c r="Y57" s="1"/>
       <x:c r="Z57" s="1"/>
     </x:row>
-    <x:row r="58" ht="18" customHeight="1">
+    <x:row r="58" spans="1:26" ht="18" customHeight="1">
       <x:c r="A58" s="2"/>
       <x:c r="B58" s="2"/>
       <x:c r="C58" s="2"/>
@@ -1841,7 +2476,7 @@
       <x:c r="Y58" s="1"/>
       <x:c r="Z58" s="1"/>
     </x:row>
-    <x:row r="59" ht="18" customHeight="1">
+    <x:row r="59" spans="1:26" ht="18" customHeight="1">
       <x:c r="A59" s="2"/>
       <x:c r="B59" s="2"/>
       <x:c r="C59" s="2"/>
@@ -1869,7 +2504,7 @@
       <x:c r="Y59" s="1"/>
       <x:c r="Z59" s="1"/>
     </x:row>
-    <x:row r="60" ht="18" customHeight="1">
+    <x:row r="60" spans="1:26" ht="18" customHeight="1">
       <x:c r="A60" s="2"/>
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
@@ -1897,7 +2532,7 @@
       <x:c r="Y60" s="1"/>
       <x:c r="Z60" s="1"/>
     </x:row>
-    <x:row r="61" ht="18" customHeight="1">
+    <x:row r="61" spans="1:26" ht="18" customHeight="1">
       <x:c r="A61" s="2"/>
       <x:c r="B61" s="2"/>
       <x:c r="C61" s="2"/>
@@ -1925,7 +2560,7 @@
       <x:c r="Y61" s="1"/>
       <x:c r="Z61" s="1"/>
     </x:row>
-    <x:row r="62" ht="18" customHeight="1">
+    <x:row r="62" spans="1:26" ht="18" customHeight="1">
       <x:c r="A62" s="2"/>
       <x:c r="B62" s="2"/>
       <x:c r="C62" s="2"/>
@@ -1953,7 +2588,7 @@
       <x:c r="Y62" s="1"/>
       <x:c r="Z62" s="1"/>
     </x:row>
-    <x:row r="63" ht="18" customHeight="1">
+    <x:row r="63" spans="1:26" ht="18" customHeight="1">
       <x:c r="A63" s="2"/>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -1981,7 +2616,7 @@
       <x:c r="Y63" s="1"/>
       <x:c r="Z63" s="1"/>
     </x:row>
-    <x:row r="64" ht="18" customHeight="1">
+    <x:row r="64" spans="1:26" ht="18" customHeight="1">
       <x:c r="A64" s="2"/>
       <x:c r="B64" s="2"/>
       <x:c r="C64" s="2"/>
@@ -2009,7 +2644,7 @@
       <x:c r="Y64" s="1"/>
       <x:c r="Z64" s="1"/>
     </x:row>
-    <x:row r="65" ht="18" customHeight="1">
+    <x:row r="65" spans="1:26" ht="18" customHeight="1">
       <x:c r="A65" s="2"/>
       <x:c r="B65" s="2"/>
       <x:c r="C65" s="2"/>
@@ -2037,7 +2672,7 @@
       <x:c r="Y65" s="1"/>
       <x:c r="Z65" s="1"/>
     </x:row>
-    <x:row r="66" ht="18" customHeight="1">
+    <x:row r="66" spans="1:26" ht="18" customHeight="1">
       <x:c r="A66" s="2"/>
       <x:c r="B66" s="2"/>
       <x:c r="C66" s="2"/>
@@ -2065,7 +2700,7 @@
       <x:c r="Y66" s="1"/>
       <x:c r="Z66" s="1"/>
     </x:row>
-    <x:row r="67" ht="18" customHeight="1">
+    <x:row r="67" spans="1:26" ht="18" customHeight="1">
       <x:c r="A67" s="5"/>
       <x:c r="B67" s="5"/>
       <x:c r="C67" s="5"/>
@@ -2093,7 +2728,7 @@
       <x:c r="Y67" s="1"/>
       <x:c r="Z67" s="1"/>
     </x:row>
-    <x:row r="68" ht="18" customHeight="1">
+    <x:row r="68" spans="1:26" ht="18" customHeight="1">
       <x:c r="A68" s="5"/>
       <x:c r="B68" s="5"/>
       <x:c r="C68" s="5"/>
@@ -2121,7 +2756,7 @@
       <x:c r="Y68" s="1"/>
       <x:c r="Z68" s="1"/>
     </x:row>
-    <x:row r="69" ht="18" customHeight="1">
+    <x:row r="69" spans="1:26" ht="18" customHeight="1">
       <x:c r="A69" s="5"/>
       <x:c r="B69" s="5"/>
       <x:c r="C69" s="5"/>
@@ -2149,7 +2784,7 @@
       <x:c r="Y69" s="1"/>
       <x:c r="Z69" s="1"/>
     </x:row>
-    <x:row r="70" ht="18" customHeight="1">
+    <x:row r="70" spans="1:26" ht="18" customHeight="1">
       <x:c r="A70" s="5"/>
       <x:c r="B70" s="5"/>
       <x:c r="C70" s="5"/>
@@ -2177,7 +2812,7 @@
       <x:c r="Y70" s="1"/>
       <x:c r="Z70" s="1"/>
     </x:row>
-    <x:row r="71" ht="18" customHeight="1">
+    <x:row r="71" spans="1:26" ht="18" customHeight="1">
       <x:c r="A71" s="5"/>
       <x:c r="B71" s="5"/>
       <x:c r="C71" s="5"/>
@@ -2205,7 +2840,7 @@
       <x:c r="Y71" s="1"/>
       <x:c r="Z71" s="1"/>
     </x:row>
-    <x:row r="72" ht="18" customHeight="1">
+    <x:row r="72" spans="1:26" ht="18" customHeight="1">
       <x:c r="A72" s="5"/>
       <x:c r="B72" s="5"/>
       <x:c r="C72" s="5"/>
@@ -2233,7 +2868,7 @@
       <x:c r="Y72" s="1"/>
       <x:c r="Z72" s="1"/>
     </x:row>
-    <x:row r="73" ht="18" customHeight="1">
+    <x:row r="73" spans="1:26" ht="18" customHeight="1">
       <x:c r="A73" s="5"/>
       <x:c r="B73" s="5"/>
       <x:c r="C73" s="5"/>
@@ -2261,7 +2896,7 @@
       <x:c r="Y73" s="1"/>
       <x:c r="Z73" s="1"/>
     </x:row>
-    <x:row r="74" ht="18" customHeight="1">
+    <x:row r="74" spans="1:26" ht="18" customHeight="1">
       <x:c r="A74" s="5"/>
       <x:c r="B74" s="5"/>
       <x:c r="C74" s="5"/>
@@ -2289,7 +2924,7 @@
       <x:c r="Y74" s="1"/>
       <x:c r="Z74" s="1"/>
     </x:row>
-    <x:row r="75" ht="18" customHeight="1">
+    <x:row r="75" spans="1:26" ht="18" customHeight="1">
       <x:c r="A75" s="5"/>
       <x:c r="B75" s="5"/>
       <x:c r="C75" s="5"/>
@@ -2317,7 +2952,7 @@
       <x:c r="Y75" s="1"/>
       <x:c r="Z75" s="1"/>
     </x:row>
-    <x:row r="76" ht="18" customHeight="1">
+    <x:row r="76" spans="1:26" ht="18" customHeight="1">
       <x:c r="A76" s="5"/>
       <x:c r="B76" s="5"/>
       <x:c r="C76" s="5"/>
@@ -2345,7 +2980,7 @@
       <x:c r="Y76" s="1"/>
       <x:c r="Z76" s="1"/>
     </x:row>
-    <x:row r="77" ht="18" customHeight="1">
+    <x:row r="77" spans="1:26" ht="18" customHeight="1">
       <x:c r="A77" s="5"/>
       <x:c r="B77" s="5"/>
       <x:c r="C77" s="5"/>
@@ -2373,7 +3008,7 @@
       <x:c r="Y77" s="1"/>
       <x:c r="Z77" s="1"/>
     </x:row>
-    <x:row r="78" ht="18" customHeight="1">
+    <x:row r="78" spans="1:26" ht="18" customHeight="1">
       <x:c r="A78" s="5"/>
       <x:c r="B78" s="5"/>
       <x:c r="C78" s="5"/>
@@ -2401,7 +3036,7 @@
       <x:c r="Y78" s="1"/>
       <x:c r="Z78" s="1"/>
     </x:row>
-    <x:row r="79" ht="18" customHeight="1">
+    <x:row r="79" spans="1:26" ht="18" customHeight="1">
       <x:c r="A79" s="5"/>
       <x:c r="B79" s="5"/>
       <x:c r="C79" s="5"/>
@@ -2429,7 +3064,7 @@
       <x:c r="Y79" s="1"/>
       <x:c r="Z79" s="1"/>
     </x:row>
-    <x:row r="80" ht="18" customHeight="1">
+    <x:row r="80" spans="1:26" ht="18" customHeight="1">
       <x:c r="A80" s="5"/>
       <x:c r="B80" s="5"/>
       <x:c r="C80" s="5"/>
@@ -2457,7 +3092,7 @@
       <x:c r="Y80" s="1"/>
       <x:c r="Z80" s="1"/>
     </x:row>
-    <x:row r="81" ht="18" customHeight="1">
+    <x:row r="81" spans="1:26" ht="18" customHeight="1">
       <x:c r="A81" s="5"/>
       <x:c r="B81" s="5"/>
       <x:c r="C81" s="5"/>
@@ -2485,7 +3120,7 @@
       <x:c r="Y81" s="1"/>
       <x:c r="Z81" s="1"/>
     </x:row>
-    <x:row r="82" ht="18" customHeight="1">
+    <x:row r="82" spans="1:26" ht="18" customHeight="1">
       <x:c r="A82" s="5"/>
       <x:c r="B82" s="5"/>
       <x:c r="C82" s="5"/>
@@ -2513,7 +3148,7 @@
       <x:c r="Y82" s="1"/>
       <x:c r="Z82" s="1"/>
     </x:row>
-    <x:row r="83" ht="18" customHeight="1">
+    <x:row r="83" spans="1:26" ht="18" customHeight="1">
       <x:c r="A83" s="5"/>
       <x:c r="B83" s="5"/>
       <x:c r="C83" s="5"/>
@@ -2541,7 +3176,7 @@
       <x:c r="Y83" s="1"/>
       <x:c r="Z83" s="1"/>
     </x:row>
-    <x:row r="84" ht="18" customHeight="1">
+    <x:row r="84" spans="1:26" ht="18" customHeight="1">
       <x:c r="A84" s="5"/>
       <x:c r="B84" s="5"/>
       <x:c r="C84" s="5"/>
@@ -2569,7 +3204,7 @@
       <x:c r="Y84" s="1"/>
       <x:c r="Z84" s="1"/>
     </x:row>
-    <x:row r="85" ht="18" customHeight="1">
+    <x:row r="85" spans="1:26" ht="18" customHeight="1">
       <x:c r="A85" s="5"/>
       <x:c r="B85" s="5"/>
       <x:c r="C85" s="5"/>
@@ -2597,7 +3232,7 @@
       <x:c r="Y85" s="1"/>
       <x:c r="Z85" s="1"/>
     </x:row>
-    <x:row r="86" ht="18" customHeight="1">
+    <x:row r="86" spans="1:26" ht="18" customHeight="1">
       <x:c r="A86" s="5"/>
       <x:c r="B86" s="5"/>
       <x:c r="C86" s="5"/>
@@ -2625,7 +3260,7 @@
       <x:c r="Y86" s="1"/>
       <x:c r="Z86" s="1"/>
     </x:row>
-    <x:row r="87" ht="18" customHeight="1">
+    <x:row r="87" spans="1:26" ht="18" customHeight="1">
       <x:c r="A87" s="5"/>
       <x:c r="B87" s="5"/>
       <x:c r="C87" s="5"/>
@@ -2653,7 +3288,7 @@
       <x:c r="Y87" s="1"/>
       <x:c r="Z87" s="1"/>
     </x:row>
-    <x:row r="88" ht="18" customHeight="1">
+    <x:row r="88" spans="1:26" ht="18" customHeight="1">
       <x:c r="A88" s="5"/>
       <x:c r="B88" s="5"/>
       <x:c r="C88" s="5"/>
@@ -2681,7 +3316,7 @@
       <x:c r="Y88" s="1"/>
       <x:c r="Z88" s="1"/>
     </x:row>
-    <x:row r="89" ht="18" customHeight="1">
+    <x:row r="89" spans="1:26" ht="18" customHeight="1">
       <x:c r="A89" s="5"/>
       <x:c r="B89" s="5"/>
       <x:c r="C89" s="5"/>
@@ -2709,7 +3344,7 @@
       <x:c r="Y89" s="1"/>
       <x:c r="Z89" s="1"/>
     </x:row>
-    <x:row r="90" ht="18" customHeight="1">
+    <x:row r="90" spans="1:26" ht="18" customHeight="1">
       <x:c r="A90" s="5"/>
       <x:c r="B90" s="5"/>
       <x:c r="C90" s="5"/>
@@ -2737,7 +3372,7 @@
       <x:c r="Y90" s="1"/>
       <x:c r="Z90" s="1"/>
     </x:row>
-    <x:row r="91" ht="18" customHeight="1">
+    <x:row r="91" spans="1:26" ht="18" customHeight="1">
       <x:c r="A91" s="5"/>
       <x:c r="B91" s="5"/>
       <x:c r="C91" s="5"/>
@@ -2765,7 +3400,7 @@
       <x:c r="Y91" s="1"/>
       <x:c r="Z91" s="1"/>
     </x:row>
-    <x:row r="92" ht="18" customHeight="1">
+    <x:row r="92" spans="1:26" ht="18" customHeight="1">
       <x:c r="A92" s="5"/>
       <x:c r="B92" s="5"/>
       <x:c r="C92" s="5"/>
@@ -2793,7 +3428,7 @@
       <x:c r="Y92" s="1"/>
       <x:c r="Z92" s="1"/>
     </x:row>
-    <x:row r="93" ht="18" customHeight="1">
+    <x:row r="93" spans="1:26" ht="18" customHeight="1">
       <x:c r="A93" s="5"/>
       <x:c r="B93" s="5"/>
       <x:c r="C93" s="5"/>
@@ -2821,7 +3456,7 @@
       <x:c r="Y93" s="1"/>
       <x:c r="Z93" s="1"/>
     </x:row>
-    <x:row r="94" ht="18" customHeight="1">
+    <x:row r="94" spans="1:26" ht="18" customHeight="1">
       <x:c r="A94" s="5"/>
       <x:c r="B94" s="5"/>
       <x:c r="C94" s="5"/>
@@ -2849,7 +3484,7 @@
       <x:c r="Y94" s="1"/>
       <x:c r="Z94" s="1"/>
     </x:row>
-    <x:row r="95" ht="18" customHeight="1">
+    <x:row r="95" spans="1:26" ht="18" customHeight="1">
       <x:c r="A95" s="5"/>
       <x:c r="B95" s="5"/>
       <x:c r="C95" s="5"/>
@@ -2877,7 +3512,7 @@
       <x:c r="Y95" s="1"/>
       <x:c r="Z95" s="1"/>
     </x:row>
-    <x:row r="96" ht="18" customHeight="1">
+    <x:row r="96" spans="1:26" ht="18" customHeight="1">
       <x:c r="A96" s="5"/>
       <x:c r="B96" s="5"/>
       <x:c r="C96" s="5"/>
@@ -2905,7 +3540,7 @@
       <x:c r="Y96" s="1"/>
       <x:c r="Z96" s="1"/>
     </x:row>
-    <x:row r="97" ht="18" customHeight="1">
+    <x:row r="97" spans="1:26" ht="18" customHeight="1">
       <x:c r="A97" s="5"/>
       <x:c r="B97" s="5"/>
       <x:c r="C97" s="5"/>
@@ -2933,7 +3568,7 @@
       <x:c r="Y97" s="1"/>
       <x:c r="Z97" s="1"/>
     </x:row>
-    <x:row r="98" ht="18" customHeight="1">
+    <x:row r="98" spans="1:26" ht="18" customHeight="1">
       <x:c r="A98" s="5"/>
       <x:c r="B98" s="5"/>
       <x:c r="C98" s="5"/>
@@ -2961,7 +3596,7 @@
       <x:c r="Y98" s="1"/>
       <x:c r="Z98" s="1"/>
     </x:row>
-    <x:row r="99" ht="18" customHeight="1">
+    <x:row r="99" spans="1:26" ht="18" customHeight="1">
       <x:c r="A99" s="5"/>
       <x:c r="B99" s="5"/>
       <x:c r="C99" s="5"/>
@@ -2989,7 +3624,7 @@
       <x:c r="Y99" s="1"/>
       <x:c r="Z99" s="1"/>
     </x:row>
-    <x:row r="100" ht="18" customHeight="1">
+    <x:row r="100" spans="1:26" ht="18" customHeight="1">
       <x:c r="A100" s="5"/>
       <x:c r="B100" s="5"/>
       <x:c r="C100" s="5"/>
@@ -3017,7 +3652,7 @@
       <x:c r="Y100" s="1"/>
       <x:c r="Z100" s="1"/>
     </x:row>
-    <x:row r="101" ht="18" customHeight="1">
+    <x:row r="101" spans="1:26" ht="18" customHeight="1">
       <x:c r="A101" s="5"/>
       <x:c r="B101" s="5"/>
       <x:c r="C101" s="5"/>
@@ -3045,7 +3680,7 @@
       <x:c r="Y101" s="1"/>
       <x:c r="Z101" s="1"/>
     </x:row>
-    <x:row r="102" ht="18" customHeight="1">
+    <x:row r="102" spans="1:26" ht="18" customHeight="1">
       <x:c r="A102" s="5"/>
       <x:c r="B102" s="5"/>
       <x:c r="C102" s="5"/>
@@ -3073,7 +3708,7 @@
       <x:c r="Y102" s="1"/>
       <x:c r="Z102" s="1"/>
     </x:row>
-    <x:row r="103" ht="18" customHeight="1">
+    <x:row r="103" spans="1:26" ht="18" customHeight="1">
       <x:c r="A103" s="5"/>
       <x:c r="B103" s="5"/>
       <x:c r="C103" s="5"/>
@@ -3101,7 +3736,7 @@
       <x:c r="Y103" s="1"/>
       <x:c r="Z103" s="1"/>
     </x:row>
-    <x:row r="104" ht="18" customHeight="1">
+    <x:row r="104" spans="1:26" ht="18" customHeight="1">
       <x:c r="A104" s="5"/>
       <x:c r="B104" s="5"/>
       <x:c r="C104" s="5"/>
@@ -3129,7 +3764,7 @@
       <x:c r="Y104" s="1"/>
       <x:c r="Z104" s="1"/>
     </x:row>
-    <x:row r="105" ht="18" customHeight="1">
+    <x:row r="105" spans="1:26" ht="18" customHeight="1">
       <x:c r="A105" s="5"/>
       <x:c r="B105" s="5"/>
       <x:c r="C105" s="5"/>
@@ -3157,7 +3792,7 @@
       <x:c r="Y105" s="1"/>
       <x:c r="Z105" s="1"/>
     </x:row>
-    <x:row r="106" ht="18" customHeight="1">
+    <x:row r="106" spans="1:26" ht="18" customHeight="1">
       <x:c r="A106" s="5"/>
       <x:c r="B106" s="5"/>
       <x:c r="C106" s="5"/>
@@ -3185,7 +3820,7 @@
       <x:c r="Y106" s="1"/>
       <x:c r="Z106" s="1"/>
     </x:row>
-    <x:row r="107" ht="18" customHeight="1">
+    <x:row r="107" spans="1:26" ht="18" customHeight="1">
       <x:c r="A107" s="5"/>
       <x:c r="B107" s="5"/>
       <x:c r="C107" s="5"/>
@@ -3213,7 +3848,7 @@
       <x:c r="Y107" s="1"/>
       <x:c r="Z107" s="1"/>
     </x:row>
-    <x:row r="108" ht="18" customHeight="1">
+    <x:row r="108" spans="1:26" ht="18" customHeight="1">
       <x:c r="A108" s="5"/>
       <x:c r="B108" s="5"/>
       <x:c r="C108" s="5"/>
@@ -3241,7 +3876,7 @@
       <x:c r="Y108" s="1"/>
       <x:c r="Z108" s="1"/>
     </x:row>
-    <x:row r="109" ht="18" customHeight="1">
+    <x:row r="109" spans="1:26" ht="18" customHeight="1">
       <x:c r="A109" s="5"/>
       <x:c r="B109" s="5"/>
       <x:c r="C109" s="5"/>
@@ -3269,7 +3904,7 @@
       <x:c r="Y109" s="1"/>
       <x:c r="Z109" s="1"/>
     </x:row>
-    <x:row r="110" ht="18" customHeight="1">
+    <x:row r="110" spans="1:26" ht="18" customHeight="1">
       <x:c r="A110" s="5"/>
       <x:c r="B110" s="5"/>
       <x:c r="C110" s="5"/>
@@ -3297,7 +3932,7 @@
       <x:c r="Y110" s="1"/>
       <x:c r="Z110" s="1"/>
     </x:row>
-    <x:row r="111" ht="18" customHeight="1">
+    <x:row r="111" spans="1:26" ht="18" customHeight="1">
       <x:c r="A111" s="5"/>
       <x:c r="B111" s="5"/>
       <x:c r="C111" s="5"/>
@@ -3325,7 +3960,7 @@
       <x:c r="Y111" s="1"/>
       <x:c r="Z111" s="1"/>
     </x:row>
-    <x:row r="112" ht="18" customHeight="1">
+    <x:row r="112" spans="1:26" ht="18" customHeight="1">
       <x:c r="A112" s="5"/>
       <x:c r="B112" s="5"/>
       <x:c r="C112" s="5"/>
@@ -3353,7 +3988,7 @@
       <x:c r="Y112" s="1"/>
       <x:c r="Z112" s="1"/>
     </x:row>
-    <x:row r="113" ht="18" customHeight="1">
+    <x:row r="113" spans="1:26" ht="18" customHeight="1">
       <x:c r="A113" s="5"/>
       <x:c r="B113" s="5"/>
       <x:c r="C113" s="5"/>
@@ -3381,7 +4016,7 @@
       <x:c r="Y113" s="1"/>
       <x:c r="Z113" s="1"/>
     </x:row>
-    <x:row r="114" ht="18" customHeight="1">
+    <x:row r="114" spans="1:26" ht="18" customHeight="1">
       <x:c r="A114" s="5"/>
       <x:c r="B114" s="5"/>
       <x:c r="C114" s="5"/>
@@ -3409,7 +4044,7 @@
       <x:c r="Y114" s="1"/>
       <x:c r="Z114" s="1"/>
     </x:row>
-    <x:row r="115" ht="18" customHeight="1">
+    <x:row r="115" spans="1:26" ht="18" customHeight="1">
       <x:c r="A115" s="5"/>
       <x:c r="B115" s="5"/>
       <x:c r="C115" s="5"/>
@@ -3437,7 +4072,7 @@
       <x:c r="Y115" s="1"/>
       <x:c r="Z115" s="1"/>
     </x:row>
-    <x:row r="116" ht="18" customHeight="1">
+    <x:row r="116" spans="1:26" ht="18" customHeight="1">
       <x:c r="A116" s="5"/>
       <x:c r="B116" s="5"/>
       <x:c r="C116" s="5"/>
@@ -3465,7 +4100,7 @@
       <x:c r="Y116" s="1"/>
       <x:c r="Z116" s="1"/>
     </x:row>
-    <x:row r="117" ht="18" customHeight="1">
+    <x:row r="117" spans="1:26" ht="18" customHeight="1">
       <x:c r="A117" s="5"/>
       <x:c r="B117" s="5"/>
       <x:c r="C117" s="5"/>
@@ -3493,7 +4128,7 @@
       <x:c r="Y117" s="1"/>
       <x:c r="Z117" s="1"/>
     </x:row>
-    <x:row r="118" ht="18" customHeight="1">
+    <x:row r="118" spans="1:26" ht="18" customHeight="1">
       <x:c r="A118" s="5"/>
       <x:c r="B118" s="5"/>
       <x:c r="C118" s="5"/>
@@ -3521,7 +4156,7 @@
       <x:c r="Y118" s="1"/>
       <x:c r="Z118" s="1"/>
     </x:row>
-    <x:row r="119" ht="18" customHeight="1">
+    <x:row r="119" spans="1:26" ht="18" customHeight="1">
       <x:c r="A119" s="5"/>
       <x:c r="B119" s="5"/>
       <x:c r="C119" s="5"/>
@@ -3549,7 +4184,7 @@
       <x:c r="Y119" s="1"/>
       <x:c r="Z119" s="1"/>
     </x:row>
-    <x:row r="120" ht="18" customHeight="1">
+    <x:row r="120" spans="1:26" ht="18" customHeight="1">
       <x:c r="A120" s="5"/>
       <x:c r="B120" s="5"/>
       <x:c r="C120" s="5"/>
@@ -3577,7 +4212,7 @@
       <x:c r="Y120" s="1"/>
       <x:c r="Z120" s="1"/>
     </x:row>
-    <x:row r="121" ht="18" customHeight="1">
+    <x:row r="121" spans="1:26" ht="18" customHeight="1">
       <x:c r="A121" s="5"/>
       <x:c r="B121" s="5"/>
       <x:c r="C121" s="5"/>
@@ -3605,7 +4240,7 @@
       <x:c r="Y121" s="1"/>
       <x:c r="Z121" s="1"/>
     </x:row>
-    <x:row r="122" ht="18" customHeight="1">
+    <x:row r="122" spans="1:26" ht="18" customHeight="1">
       <x:c r="A122" s="5"/>
       <x:c r="B122" s="5"/>
       <x:c r="C122" s="5"/>
@@ -3633,7 +4268,7 @@
       <x:c r="Y122" s="1"/>
       <x:c r="Z122" s="1"/>
     </x:row>
-    <x:row r="123" ht="18" customHeight="1">
+    <x:row r="123" spans="1:26" ht="18" customHeight="1">
       <x:c r="A123" s="5"/>
       <x:c r="B123" s="5"/>
       <x:c r="C123" s="5"/>
@@ -3661,7 +4296,7 @@
       <x:c r="Y123" s="1"/>
       <x:c r="Z123" s="1"/>
     </x:row>
-    <x:row r="124" ht="18" customHeight="1">
+    <x:row r="124" spans="1:26" ht="18" customHeight="1">
       <x:c r="A124" s="5"/>
       <x:c r="B124" s="5"/>
       <x:c r="C124" s="5"/>
@@ -3689,7 +4324,7 @@
       <x:c r="Y124" s="1"/>
       <x:c r="Z124" s="1"/>
     </x:row>
-    <x:row r="125" ht="18" customHeight="1">
+    <x:row r="125" spans="1:26" ht="18" customHeight="1">
       <x:c r="A125" s="5"/>
       <x:c r="B125" s="5"/>
       <x:c r="C125" s="5"/>
@@ -3717,7 +4352,7 @@
       <x:c r="Y125" s="1"/>
       <x:c r="Z125" s="1"/>
     </x:row>
-    <x:row r="126" ht="18" customHeight="1">
+    <x:row r="126" spans="1:26" ht="18" customHeight="1">
       <x:c r="A126" s="5"/>
       <x:c r="B126" s="5"/>
       <x:c r="C126" s="5"/>
@@ -3745,7 +4380,7 @@
       <x:c r="Y126" s="1"/>
       <x:c r="Z126" s="1"/>
     </x:row>
-    <x:row r="127" ht="18" customHeight="1">
+    <x:row r="127" spans="1:26" ht="18" customHeight="1">
       <x:c r="A127" s="5"/>
       <x:c r="B127" s="5"/>
       <x:c r="C127" s="5"/>
@@ -3773,7 +4408,7 @@
       <x:c r="Y127" s="1"/>
       <x:c r="Z127" s="1"/>
     </x:row>
-    <x:row r="128" ht="18" customHeight="1">
+    <x:row r="128" spans="1:26" ht="18" customHeight="1">
       <x:c r="A128" s="5"/>
       <x:c r="B128" s="5"/>
       <x:c r="C128" s="5"/>
@@ -3801,7 +4436,7 @@
       <x:c r="Y128" s="1"/>
       <x:c r="Z128" s="1"/>
     </x:row>
-    <x:row r="129" ht="18" customHeight="1">
+    <x:row r="129" spans="1:26" ht="18" customHeight="1">
       <x:c r="A129" s="5"/>
       <x:c r="B129" s="5"/>
       <x:c r="C129" s="5"/>
@@ -3829,7 +4464,7 @@
       <x:c r="Y129" s="1"/>
       <x:c r="Z129" s="1"/>
     </x:row>
-    <x:row r="130" ht="18" customHeight="1">
+    <x:row r="130" spans="1:26" ht="18" customHeight="1">
       <x:c r="A130" s="5"/>
       <x:c r="B130" s="5"/>
       <x:c r="C130" s="5"/>
@@ -3857,7 +4492,7 @@
       <x:c r="Y130" s="1"/>
       <x:c r="Z130" s="1"/>
     </x:row>
-    <x:row r="131" ht="18" customHeight="1">
+    <x:row r="131" spans="1:26" ht="18" customHeight="1">
       <x:c r="A131" s="5"/>
       <x:c r="B131" s="5"/>
       <x:c r="C131" s="5"/>
@@ -3885,7 +4520,7 @@
       <x:c r="Y131" s="1"/>
       <x:c r="Z131" s="1"/>
     </x:row>
-    <x:row r="132" ht="18" customHeight="1">
+    <x:row r="132" spans="1:26" ht="18" customHeight="1">
       <x:c r="A132" s="5"/>
       <x:c r="B132" s="5"/>
       <x:c r="C132" s="5"/>
@@ -3913,7 +4548,7 @@
       <x:c r="Y132" s="1"/>
       <x:c r="Z132" s="1"/>
     </x:row>
-    <x:row r="133" ht="18" customHeight="1">
+    <x:row r="133" spans="1:26" ht="18" customHeight="1">
       <x:c r="A133" s="5"/>
       <x:c r="B133" s="5"/>
       <x:c r="C133" s="5"/>
@@ -3941,7 +4576,7 @@
       <x:c r="Y133" s="1"/>
       <x:c r="Z133" s="1"/>
     </x:row>
-    <x:row r="134" ht="18" customHeight="1">
+    <x:row r="134" spans="1:26" ht="18" customHeight="1">
       <x:c r="A134" s="5"/>
       <x:c r="B134" s="5"/>
       <x:c r="C134" s="5"/>
@@ -3969,7 +4604,7 @@
       <x:c r="Y134" s="1"/>
       <x:c r="Z134" s="1"/>
     </x:row>
-    <x:row r="135" ht="18" customHeight="1">
+    <x:row r="135" spans="1:26" ht="18" customHeight="1">
       <x:c r="A135" s="5"/>
       <x:c r="B135" s="5"/>
       <x:c r="C135" s="5"/>
@@ -3997,7 +4632,7 @@
       <x:c r="Y135" s="1"/>
       <x:c r="Z135" s="1"/>
     </x:row>
-    <x:row r="136" ht="18" customHeight="1">
+    <x:row r="136" spans="1:26" ht="18" customHeight="1">
       <x:c r="A136" s="5"/>
       <x:c r="B136" s="5"/>
       <x:c r="C136" s="5"/>
@@ -4025,7 +4660,7 @@
       <x:c r="Y136" s="1"/>
       <x:c r="Z136" s="1"/>
     </x:row>
-    <x:row r="137" ht="18" customHeight="1">
+    <x:row r="137" spans="1:26" ht="18" customHeight="1">
       <x:c r="A137" s="5"/>
       <x:c r="B137" s="5"/>
       <x:c r="C137" s="5"/>
@@ -4053,7 +4688,7 @@
       <x:c r="Y137" s="1"/>
       <x:c r="Z137" s="1"/>
     </x:row>
-    <x:row r="138" ht="18" customHeight="1">
+    <x:row r="138" spans="1:26" ht="18" customHeight="1">
       <x:c r="A138" s="5"/>
       <x:c r="B138" s="5"/>
       <x:c r="C138" s="5"/>
@@ -4081,7 +4716,7 @@
       <x:c r="Y138" s="1"/>
       <x:c r="Z138" s="1"/>
     </x:row>
-    <x:row r="139" ht="18" customHeight="1">
+    <x:row r="139" spans="1:26" ht="18" customHeight="1">
       <x:c r="A139" s="5"/>
       <x:c r="B139" s="5"/>
       <x:c r="C139" s="5"/>
@@ -4109,7 +4744,7 @@
       <x:c r="Y139" s="1"/>
       <x:c r="Z139" s="1"/>
     </x:row>
-    <x:row r="140" ht="18" customHeight="1">
+    <x:row r="140" spans="1:26" ht="18" customHeight="1">
       <x:c r="A140" s="5"/>
       <x:c r="B140" s="5"/>
       <x:c r="C140" s="5"/>
@@ -4137,7 +4772,7 @@
       <x:c r="Y140" s="1"/>
       <x:c r="Z140" s="1"/>
     </x:row>
-    <x:row r="141" ht="18" customHeight="1">
+    <x:row r="141" spans="1:26" ht="18" customHeight="1">
       <x:c r="A141" s="5"/>
       <x:c r="B141" s="5"/>
       <x:c r="C141" s="5"/>
@@ -4165,7 +4800,7 @@
       <x:c r="Y141" s="1"/>
       <x:c r="Z141" s="1"/>
     </x:row>
-    <x:row r="142" ht="18" customHeight="1">
+    <x:row r="142" spans="1:26" ht="18" customHeight="1">
       <x:c r="A142" s="5"/>
       <x:c r="B142" s="5"/>
       <x:c r="C142" s="5"/>
@@ -4193,7 +4828,7 @@
       <x:c r="Y142" s="1"/>
       <x:c r="Z142" s="1"/>
     </x:row>
-    <x:row r="143" ht="18" customHeight="1">
+    <x:row r="143" spans="1:26" ht="18" customHeight="1">
       <x:c r="A143" s="5"/>
       <x:c r="B143" s="5"/>
       <x:c r="C143" s="5"/>
@@ -4221,7 +4856,7 @@
       <x:c r="Y143" s="1"/>
       <x:c r="Z143" s="1"/>
     </x:row>
-    <x:row r="144" ht="18" customHeight="1">
+    <x:row r="144" spans="1:26" ht="18" customHeight="1">
       <x:c r="A144" s="5"/>
       <x:c r="B144" s="5"/>
       <x:c r="C144" s="5"/>
@@ -4249,7 +4884,7 @@
       <x:c r="Y144" s="1"/>
       <x:c r="Z144" s="1"/>
     </x:row>
-    <x:row r="145" ht="18" customHeight="1">
+    <x:row r="145" spans="1:26" ht="18" customHeight="1">
       <x:c r="A145" s="5"/>
       <x:c r="B145" s="5"/>
       <x:c r="C145" s="5"/>
@@ -4277,7 +4912,7 @@
       <x:c r="Y145" s="1"/>
       <x:c r="Z145" s="1"/>
     </x:row>
-    <x:row r="146" ht="18" customHeight="1">
+    <x:row r="146" spans="1:26" ht="18" customHeight="1">
       <x:c r="A146" s="5"/>
       <x:c r="B146" s="5"/>
       <x:c r="C146" s="5"/>
@@ -4305,7 +4940,7 @@
       <x:c r="Y146" s="1"/>
       <x:c r="Z146" s="1"/>
     </x:row>
-    <x:row r="147" ht="18" customHeight="1">
+    <x:row r="147" spans="1:26" ht="18" customHeight="1">
       <x:c r="A147" s="5"/>
       <x:c r="B147" s="5"/>
       <x:c r="C147" s="5"/>
@@ -4333,7 +4968,7 @@
       <x:c r="Y147" s="1"/>
       <x:c r="Z147" s="1"/>
     </x:row>
-    <x:row r="148" ht="18" customHeight="1">
+    <x:row r="148" spans="1:26" ht="18" customHeight="1">
       <x:c r="A148" s="5"/>
       <x:c r="B148" s="5"/>
       <x:c r="C148" s="5"/>
@@ -4361,7 +4996,7 @@
       <x:c r="Y148" s="1"/>
       <x:c r="Z148" s="1"/>
     </x:row>
-    <x:row r="149" ht="18" customHeight="1">
+    <x:row r="149" spans="1:26" ht="18" customHeight="1">
       <x:c r="A149" s="5"/>
       <x:c r="B149" s="5"/>
       <x:c r="C149" s="5"/>
@@ -4389,7 +5024,7 @@
       <x:c r="Y149" s="1"/>
       <x:c r="Z149" s="1"/>
     </x:row>
-    <x:row r="150" ht="18" customHeight="1">
+    <x:row r="150" spans="1:26" ht="18" customHeight="1">
       <x:c r="A150" s="5"/>
       <x:c r="B150" s="5"/>
       <x:c r="C150" s="5"/>
@@ -4417,7 +5052,7 @@
       <x:c r="Y150" s="1"/>
       <x:c r="Z150" s="1"/>
     </x:row>
-    <x:row r="151" ht="18" customHeight="1">
+    <x:row r="151" spans="1:26" ht="18" customHeight="1">
       <x:c r="A151" s="5"/>
       <x:c r="B151" s="5"/>
       <x:c r="C151" s="5"/>
@@ -4445,7 +5080,7 @@
       <x:c r="Y151" s="1"/>
       <x:c r="Z151" s="1"/>
     </x:row>
-    <x:row r="152" ht="18" customHeight="1">
+    <x:row r="152" spans="1:26" ht="18" customHeight="1">
       <x:c r="A152" s="5"/>
       <x:c r="B152" s="5"/>
       <x:c r="C152" s="5"/>
@@ -4473,7 +5108,7 @@
       <x:c r="Y152" s="1"/>
       <x:c r="Z152" s="1"/>
     </x:row>
-    <x:row r="153" ht="18" customHeight="1">
+    <x:row r="153" spans="1:26" ht="18" customHeight="1">
       <x:c r="A153" s="5"/>
       <x:c r="B153" s="5"/>
       <x:c r="C153" s="5"/>
@@ -4501,7 +5136,7 @@
       <x:c r="Y153" s="1"/>
       <x:c r="Z153" s="1"/>
     </x:row>
-    <x:row r="154" ht="18" customHeight="1">
+    <x:row r="154" spans="1:26" ht="18" customHeight="1">
       <x:c r="A154" s="5"/>
       <x:c r="B154" s="5"/>
       <x:c r="C154" s="5"/>
@@ -4529,7 +5164,7 @@
       <x:c r="Y154" s="1"/>
       <x:c r="Z154" s="1"/>
     </x:row>
-    <x:row r="155" ht="18" customHeight="1">
+    <x:row r="155" spans="1:26" ht="18" customHeight="1">
       <x:c r="A155" s="5"/>
       <x:c r="B155" s="5"/>
       <x:c r="C155" s="5"/>
@@ -4557,7 +5192,7 @@
       <x:c r="Y155" s="1"/>
       <x:c r="Z155" s="1"/>
     </x:row>
-    <x:row r="156" ht="18" customHeight="1">
+    <x:row r="156" spans="1:26" ht="18" customHeight="1">
       <x:c r="A156" s="5"/>
       <x:c r="B156" s="5"/>
       <x:c r="C156" s="5"/>
@@ -4585,7 +5220,7 @@
       <x:c r="Y156" s="1"/>
       <x:c r="Z156" s="1"/>
     </x:row>
-    <x:row r="157" ht="18" customHeight="1">
+    <x:row r="157" spans="1:26" ht="18" customHeight="1">
       <x:c r="A157" s="5"/>
       <x:c r="B157" s="5"/>
       <x:c r="C157" s="5"/>
@@ -4613,7 +5248,7 @@
       <x:c r="Y157" s="1"/>
       <x:c r="Z157" s="1"/>
     </x:row>
-    <x:row r="158" ht="18" customHeight="1">
+    <x:row r="158" spans="1:26" ht="18" customHeight="1">
       <x:c r="A158" s="5"/>
       <x:c r="B158" s="5"/>
       <x:c r="C158" s="5"/>
@@ -4641,7 +5276,7 @@
       <x:c r="Y158" s="1"/>
       <x:c r="Z158" s="1"/>
     </x:row>
-    <x:row r="159" ht="18" customHeight="1">
+    <x:row r="159" spans="1:26" ht="18" customHeight="1">
       <x:c r="A159" s="5"/>
       <x:c r="B159" s="5"/>
       <x:c r="C159" s="5"/>
@@ -4669,7 +5304,7 @@
       <x:c r="Y159" s="1"/>
       <x:c r="Z159" s="1"/>
     </x:row>
-    <x:row r="160" ht="18" customHeight="1">
+    <x:row r="160" spans="1:26" ht="18" customHeight="1">
       <x:c r="A160" s="5"/>
       <x:c r="B160" s="5"/>
       <x:c r="C160" s="5"/>
@@ -4697,7 +5332,7 @@
       <x:c r="Y160" s="1"/>
       <x:c r="Z160" s="1"/>
     </x:row>
-    <x:row r="161" ht="18" customHeight="1">
+    <x:row r="161" spans="1:26" ht="18" customHeight="1">
       <x:c r="A161" s="5"/>
       <x:c r="B161" s="5"/>
       <x:c r="C161" s="5"/>
@@ -4725,7 +5360,7 @@
       <x:c r="Y161" s="1"/>
       <x:c r="Z161" s="1"/>
     </x:row>
-    <x:row r="162" ht="18" customHeight="1">
+    <x:row r="162" spans="1:26" ht="18" customHeight="1">
       <x:c r="A162" s="5"/>
       <x:c r="B162" s="5"/>
       <x:c r="C162" s="5"/>
@@ -4753,7 +5388,7 @@
       <x:c r="Y162" s="1"/>
       <x:c r="Z162" s="1"/>
     </x:row>
-    <x:row r="163" ht="18" customHeight="1">
+    <x:row r="163" spans="1:26" ht="18" customHeight="1">
       <x:c r="A163" s="5"/>
       <x:c r="B163" s="5"/>
       <x:c r="C163" s="5"/>
@@ -4781,7 +5416,7 @@
       <x:c r="Y163" s="1"/>
       <x:c r="Z163" s="1"/>
     </x:row>
-    <x:row r="164" ht="18" customHeight="1">
+    <x:row r="164" spans="1:26" ht="18" customHeight="1">
       <x:c r="A164" s="5"/>
       <x:c r="B164" s="5"/>
       <x:c r="C164" s="5"/>
@@ -4809,7 +5444,7 @@
       <x:c r="Y164" s="1"/>
       <x:c r="Z164" s="1"/>
     </x:row>
-    <x:row r="165" ht="18" customHeight="1">
+    <x:row r="165" spans="1:26" ht="18" customHeight="1">
       <x:c r="A165" s="5"/>
       <x:c r="B165" s="5"/>
       <x:c r="C165" s="5"/>
@@ -4837,7 +5472,7 @@
       <x:c r="Y165" s="1"/>
       <x:c r="Z165" s="1"/>
     </x:row>
-    <x:row r="166" ht="18" customHeight="1">
+    <x:row r="166" spans="1:26" ht="18" customHeight="1">
       <x:c r="A166" s="5"/>
       <x:c r="B166" s="5"/>
       <x:c r="C166" s="5"/>
@@ -4865,7 +5500,7 @@
       <x:c r="Y166" s="1"/>
       <x:c r="Z166" s="1"/>
     </x:row>
-    <x:row r="167" ht="18" customHeight="1">
+    <x:row r="167" spans="1:26" ht="18" customHeight="1">
       <x:c r="A167" s="5"/>
       <x:c r="B167" s="5"/>
       <x:c r="C167" s="5"/>
@@ -4893,7 +5528,7 @@
       <x:c r="Y167" s="1"/>
       <x:c r="Z167" s="1"/>
     </x:row>
-    <x:row r="168" ht="18" customHeight="1">
+    <x:row r="168" spans="1:26" ht="18" customHeight="1">
       <x:c r="A168" s="5"/>
       <x:c r="B168" s="5"/>
       <x:c r="C168" s="5"/>
@@ -4921,7 +5556,7 @@
       <x:c r="Y168" s="1"/>
       <x:c r="Z168" s="1"/>
     </x:row>
-    <x:row r="169" ht="18" customHeight="1">
+    <x:row r="169" spans="1:26" ht="18" customHeight="1">
       <x:c r="A169" s="5"/>
       <x:c r="B169" s="5"/>
       <x:c r="C169" s="5"/>
@@ -4949,7 +5584,7 @@
       <x:c r="Y169" s="1"/>
       <x:c r="Z169" s="1"/>
     </x:row>
-    <x:row r="170" ht="18" customHeight="1">
+    <x:row r="170" spans="1:26" ht="18" customHeight="1">
       <x:c r="A170" s="5"/>
       <x:c r="B170" s="5"/>
       <x:c r="C170" s="5"/>
@@ -4977,7 +5612,7 @@
       <x:c r="Y170" s="1"/>
       <x:c r="Z170" s="1"/>
     </x:row>
-    <x:row r="171" ht="18" customHeight="1">
+    <x:row r="171" spans="1:26" ht="18" customHeight="1">
       <x:c r="A171" s="5"/>
       <x:c r="B171" s="5"/>
       <x:c r="C171" s="5"/>
@@ -5005,7 +5640,7 @@
       <x:c r="Y171" s="1"/>
       <x:c r="Z171" s="1"/>
     </x:row>
-    <x:row r="172" ht="18" customHeight="1">
+    <x:row r="172" spans="1:26" ht="18" customHeight="1">
       <x:c r="A172" s="5"/>
       <x:c r="B172" s="5"/>
       <x:c r="C172" s="5"/>
@@ -5033,7 +5668,7 @@
       <x:c r="Y172" s="1"/>
       <x:c r="Z172" s="1"/>
     </x:row>
-    <x:row r="173" ht="18" customHeight="1">
+    <x:row r="173" spans="1:26" ht="18" customHeight="1">
       <x:c r="A173" s="5"/>
       <x:c r="B173" s="5"/>
       <x:c r="C173" s="5"/>
@@ -5061,7 +5696,7 @@
       <x:c r="Y173" s="1"/>
       <x:c r="Z173" s="1"/>
     </x:row>
-    <x:row r="174" ht="18" customHeight="1">
+    <x:row r="174" spans="1:26" ht="18" customHeight="1">
       <x:c r="A174" s="5"/>
       <x:c r="B174" s="5"/>
       <x:c r="C174" s="5"/>
@@ -5089,7 +5724,7 @@
       <x:c r="Y174" s="1"/>
       <x:c r="Z174" s="1"/>
     </x:row>
-    <x:row r="175" ht="18" customHeight="1">
+    <x:row r="175" spans="1:26" ht="18" customHeight="1">
       <x:c r="A175" s="5"/>
       <x:c r="B175" s="5"/>
       <x:c r="C175" s="5"/>
@@ -5117,7 +5752,7 @@
       <x:c r="Y175" s="1"/>
       <x:c r="Z175" s="1"/>
     </x:row>
-    <x:row r="176" ht="18" customHeight="1">
+    <x:row r="176" spans="1:26" ht="18" customHeight="1">
       <x:c r="A176" s="5"/>
       <x:c r="B176" s="5"/>
       <x:c r="C176" s="5"/>
@@ -5145,7 +5780,7 @@
       <x:c r="Y176" s="1"/>
       <x:c r="Z176" s="1"/>
     </x:row>
-    <x:row r="177" ht="18" customHeight="1">
+    <x:row r="177" spans="1:26" ht="18" customHeight="1">
       <x:c r="A177" s="5"/>
       <x:c r="B177" s="5"/>
       <x:c r="C177" s="5"/>
@@ -5173,7 +5808,7 @@
       <x:c r="Y177" s="1"/>
       <x:c r="Z177" s="1"/>
     </x:row>
-    <x:row r="178" ht="18" customHeight="1">
+    <x:row r="178" spans="1:26" ht="18" customHeight="1">
       <x:c r="A178" s="5"/>
       <x:c r="B178" s="5"/>
       <x:c r="C178" s="5"/>
@@ -5201,7 +5836,7 @@
       <x:c r="Y178" s="1"/>
       <x:c r="Z178" s="1"/>
     </x:row>
-    <x:row r="179" ht="18" customHeight="1">
+    <x:row r="179" spans="1:26" ht="18" customHeight="1">
       <x:c r="A179" s="5"/>
       <x:c r="B179" s="5"/>
       <x:c r="C179" s="5"/>
@@ -5229,7 +5864,7 @@
       <x:c r="Y179" s="1"/>
       <x:c r="Z179" s="1"/>
     </x:row>
-    <x:row r="180" ht="18" customHeight="1">
+    <x:row r="180" spans="1:26" ht="18" customHeight="1">
       <x:c r="A180" s="5"/>
       <x:c r="B180" s="5"/>
       <x:c r="C180" s="5"/>
@@ -5257,7 +5892,7 @@
       <x:c r="Y180" s="1"/>
       <x:c r="Z180" s="1"/>
     </x:row>
-    <x:row r="181" ht="18" customHeight="1">
+    <x:row r="181" spans="1:26" ht="18" customHeight="1">
       <x:c r="A181" s="5"/>
       <x:c r="B181" s="5"/>
       <x:c r="C181" s="5"/>
@@ -5285,7 +5920,7 @@
       <x:c r="Y181" s="1"/>
       <x:c r="Z181" s="1"/>
     </x:row>
-    <x:row r="182" ht="18" customHeight="1">
+    <x:row r="182" spans="1:26" ht="18" customHeight="1">
       <x:c r="A182" s="5"/>
       <x:c r="B182" s="5"/>
       <x:c r="C182" s="5"/>
@@ -5313,7 +5948,7 @@
       <x:c r="Y182" s="1"/>
       <x:c r="Z182" s="1"/>
     </x:row>
-    <x:row r="183" ht="18" customHeight="1">
+    <x:row r="183" spans="1:26" ht="18" customHeight="1">
       <x:c r="A183" s="5"/>
       <x:c r="B183" s="5"/>
       <x:c r="C183" s="5"/>
@@ -5341,7 +5976,7 @@
       <x:c r="Y183" s="1"/>
       <x:c r="Z183" s="1"/>
     </x:row>
-    <x:row r="184" ht="18" customHeight="1">
+    <x:row r="184" spans="1:26" ht="18" customHeight="1">
       <x:c r="A184" s="5"/>
       <x:c r="B184" s="5"/>
       <x:c r="C184" s="5"/>
@@ -5369,7 +6004,7 @@
       <x:c r="Y184" s="1"/>
       <x:c r="Z184" s="1"/>
     </x:row>
-    <x:row r="185" ht="18" customHeight="1">
+    <x:row r="185" spans="1:26" ht="18" customHeight="1">
       <x:c r="A185" s="5"/>
       <x:c r="B185" s="5"/>
       <x:c r="C185" s="5"/>
@@ -5397,7 +6032,7 @@
       <x:c r="Y185" s="1"/>
       <x:c r="Z185" s="1"/>
     </x:row>
-    <x:row r="186" ht="18" customHeight="1">
+    <x:row r="186" spans="1:26" ht="18" customHeight="1">
       <x:c r="A186" s="5"/>
       <x:c r="B186" s="5"/>
       <x:c r="C186" s="5"/>
@@ -5425,7 +6060,7 @@
       <x:c r="Y186" s="1"/>
       <x:c r="Z186" s="1"/>
     </x:row>
-    <x:row r="187" ht="18" customHeight="1">
+    <x:row r="187" spans="1:26" ht="18" customHeight="1">
       <x:c r="A187" s="5"/>
       <x:c r="B187" s="5"/>
       <x:c r="C187" s="5"/>
@@ -5453,7 +6088,7 @@
       <x:c r="Y187" s="1"/>
       <x:c r="Z187" s="1"/>
     </x:row>
-    <x:row r="188" ht="18" customHeight="1">
+    <x:row r="188" spans="1:26" ht="18" customHeight="1">
       <x:c r="A188" s="5"/>
       <x:c r="B188" s="5"/>
       <x:c r="C188" s="5"/>
@@ -5481,7 +6116,7 @@
       <x:c r="Y188" s="1"/>
       <x:c r="Z188" s="1"/>
     </x:row>
-    <x:row r="189" ht="18" customHeight="1">
+    <x:row r="189" spans="1:26" ht="18" customHeight="1">
       <x:c r="A189" s="5"/>
       <x:c r="B189" s="5"/>
       <x:c r="C189" s="5"/>
@@ -5509,7 +6144,7 @@
       <x:c r="Y189" s="1"/>
       <x:c r="Z189" s="1"/>
     </x:row>
-    <x:row r="190" ht="18" customHeight="1">
+    <x:row r="190" spans="1:26" ht="18" customHeight="1">
       <x:c r="A190" s="5"/>
       <x:c r="B190" s="5"/>
       <x:c r="C190" s="5"/>
@@ -5537,7 +6172,7 @@
       <x:c r="Y190" s="1"/>
       <x:c r="Z190" s="1"/>
     </x:row>
-    <x:row r="191" ht="18" customHeight="1">
+    <x:row r="191" spans="1:26" ht="18" customHeight="1">
       <x:c r="A191" s="5"/>
       <x:c r="B191" s="5"/>
       <x:c r="C191" s="5"/>
@@ -5565,7 +6200,7 @@
       <x:c r="Y191" s="1"/>
       <x:c r="Z191" s="1"/>
     </x:row>
-    <x:row r="192" ht="18" customHeight="1">
+    <x:row r="192" spans="1:26" ht="18" customHeight="1">
       <x:c r="A192" s="5"/>
       <x:c r="B192" s="5"/>
       <x:c r="C192" s="5"/>
@@ -5593,7 +6228,7 @@
       <x:c r="Y192" s="1"/>
       <x:c r="Z192" s="1"/>
     </x:row>
-    <x:row r="193" ht="18" customHeight="1">
+    <x:row r="193" spans="1:26" ht="18" customHeight="1">
       <x:c r="A193" s="5"/>
       <x:c r="B193" s="5"/>
       <x:c r="C193" s="5"/>
@@ -5621,7 +6256,7 @@
       <x:c r="Y193" s="1"/>
       <x:c r="Z193" s="1"/>
     </x:row>
-    <x:row r="194" ht="18" customHeight="1">
+    <x:row r="194" spans="1:26" ht="18" customHeight="1">
       <x:c r="A194" s="5"/>
       <x:c r="B194" s="5"/>
       <x:c r="C194" s="5"/>
@@ -5649,7 +6284,7 @@
       <x:c r="Y194" s="1"/>
       <x:c r="Z194" s="1"/>
     </x:row>
-    <x:row r="195" ht="18" customHeight="1">
+    <x:row r="195" spans="1:26" ht="18" customHeight="1">
       <x:c r="A195" s="5"/>
       <x:c r="B195" s="5"/>
       <x:c r="C195" s="5"/>
@@ -5677,7 +6312,7 @@
       <x:c r="Y195" s="1"/>
       <x:c r="Z195" s="1"/>
     </x:row>
-    <x:row r="196" ht="18" customHeight="1">
+    <x:row r="196" spans="1:26" ht="18" customHeight="1">
       <x:c r="A196" s="5"/>
       <x:c r="B196" s="5"/>
       <x:c r="C196" s="5"/>
@@ -5705,7 +6340,7 @@
       <x:c r="Y196" s="1"/>
       <x:c r="Z196" s="1"/>
     </x:row>
-    <x:row r="197" ht="18" customHeight="1">
+    <x:row r="197" spans="1:26" ht="18" customHeight="1">
       <x:c r="A197" s="5"/>
       <x:c r="B197" s="5"/>
       <x:c r="C197" s="5"/>
@@ -5733,7 +6368,7 @@
       <x:c r="Y197" s="1"/>
       <x:c r="Z197" s="1"/>
     </x:row>
-    <x:row r="198" ht="18" customHeight="1">
+    <x:row r="198" spans="1:26" ht="18" customHeight="1">
       <x:c r="A198" s="5"/>
       <x:c r="B198" s="5"/>
       <x:c r="C198" s="5"/>
@@ -5761,7 +6396,7 @@
       <x:c r="Y198" s="1"/>
       <x:c r="Z198" s="1"/>
     </x:row>
-    <x:row r="199" ht="18" customHeight="1">
+    <x:row r="199" spans="1:26" ht="18" customHeight="1">
       <x:c r="A199" s="5"/>
       <x:c r="B199" s="5"/>
       <x:c r="C199" s="5"/>
@@ -5789,7 +6424,7 @@
       <x:c r="Y199" s="1"/>
       <x:c r="Z199" s="1"/>
     </x:row>
-    <x:row r="200" ht="18" customHeight="1">
+    <x:row r="200" spans="1:26" ht="18" customHeight="1">
       <x:c r="A200" s="5"/>
       <x:c r="B200" s="5"/>
       <x:c r="C200" s="5"/>
@@ -5817,7 +6452,7 @@
       <x:c r="Y200" s="1"/>
       <x:c r="Z200" s="1"/>
     </x:row>
-    <x:row r="201" ht="18" customHeight="1">
+    <x:row r="201" spans="1:26" ht="18" customHeight="1">
       <x:c r="A201" s="5"/>
       <x:c r="B201" s="5"/>
       <x:c r="C201" s="5"/>
@@ -5845,7 +6480,7 @@
       <x:c r="Y201" s="1"/>
       <x:c r="Z201" s="1"/>
     </x:row>
-    <x:row r="202" ht="18" customHeight="1">
+    <x:row r="202" spans="1:26" ht="18" customHeight="1">
       <x:c r="A202" s="5"/>
       <x:c r="B202" s="5"/>
       <x:c r="C202" s="5"/>
@@ -5873,7 +6508,7 @@
       <x:c r="Y202" s="1"/>
       <x:c r="Z202" s="1"/>
     </x:row>
-    <x:row r="203" ht="18" customHeight="1">
+    <x:row r="203" spans="1:26" ht="18" customHeight="1">
       <x:c r="A203" s="5"/>
       <x:c r="B203" s="5"/>
       <x:c r="C203" s="5"/>
@@ -5901,7 +6536,7 @@
       <x:c r="Y203" s="1"/>
       <x:c r="Z203" s="1"/>
     </x:row>
-    <x:row r="204" ht="18" customHeight="1">
+    <x:row r="204" spans="1:26" ht="18" customHeight="1">
       <x:c r="A204" s="5"/>
       <x:c r="B204" s="5"/>
       <x:c r="C204" s="5"/>
@@ -5929,7 +6564,7 @@
       <x:c r="Y204" s="1"/>
       <x:c r="Z204" s="1"/>
     </x:row>
-    <x:row r="205" ht="18" customHeight="1">
+    <x:row r="205" spans="1:26" ht="18" customHeight="1">
       <x:c r="A205" s="5"/>
       <x:c r="B205" s="5"/>
       <x:c r="C205" s="5"/>
@@ -5957,7 +6592,7 @@
       <x:c r="Y205" s="1"/>
       <x:c r="Z205" s="1"/>
     </x:row>
-    <x:row r="206" ht="18" customHeight="1">
+    <x:row r="206" spans="1:26" ht="18" customHeight="1">
       <x:c r="A206" s="5"/>
       <x:c r="B206" s="5"/>
       <x:c r="C206" s="5"/>
@@ -5985,7 +6620,7 @@
       <x:c r="Y206" s="1"/>
       <x:c r="Z206" s="1"/>
     </x:row>
-    <x:row r="207" ht="18" customHeight="1">
+    <x:row r="207" spans="1:26" ht="18" customHeight="1">
       <x:c r="A207" s="5"/>
       <x:c r="B207" s="5"/>
       <x:c r="C207" s="5"/>
@@ -6013,7 +6648,7 @@
       <x:c r="Y207" s="1"/>
       <x:c r="Z207" s="1"/>
     </x:row>
-    <x:row r="208" ht="18" customHeight="1">
+    <x:row r="208" spans="1:26" ht="18" customHeight="1">
       <x:c r="A208" s="5"/>
       <x:c r="B208" s="5"/>
       <x:c r="C208" s="5"/>
@@ -6041,7 +6676,7 @@
       <x:c r="Y208" s="1"/>
       <x:c r="Z208" s="1"/>
     </x:row>
-    <x:row r="209" ht="18" customHeight="1">
+    <x:row r="209" spans="1:26" ht="18" customHeight="1">
       <x:c r="A209" s="5"/>
       <x:c r="B209" s="5"/>
       <x:c r="C209" s="5"/>
@@ -6069,7 +6704,7 @@
       <x:c r="Y209" s="1"/>
       <x:c r="Z209" s="1"/>
     </x:row>
-    <x:row r="210" ht="18" customHeight="1">
+    <x:row r="210" spans="1:26" ht="18" customHeight="1">
       <x:c r="A210" s="5"/>
       <x:c r="B210" s="5"/>
       <x:c r="C210" s="5"/>
@@ -6097,7 +6732,7 @@
       <x:c r="Y210" s="1"/>
       <x:c r="Z210" s="1"/>
     </x:row>
-    <x:row r="211" ht="18" customHeight="1">
+    <x:row r="211" spans="1:26" ht="18" customHeight="1">
       <x:c r="A211" s="5"/>
       <x:c r="B211" s="5"/>
       <x:c r="C211" s="5"/>
@@ -6125,7 +6760,7 @@
       <x:c r="Y211" s="1"/>
       <x:c r="Z211" s="1"/>
     </x:row>
-    <x:row r="212" ht="18" customHeight="1">
+    <x:row r="212" spans="1:26" ht="18" customHeight="1">
       <x:c r="A212" s="5"/>
       <x:c r="B212" s="5"/>
       <x:c r="C212" s="5"/>
@@ -6153,7 +6788,7 @@
       <x:c r="Y212" s="1"/>
       <x:c r="Z212" s="1"/>
     </x:row>
-    <x:row r="213" ht="18" customHeight="1">
+    <x:row r="213" spans="1:26" ht="18" customHeight="1">
       <x:c r="A213" s="5"/>
       <x:c r="B213" s="5"/>
       <x:c r="C213" s="5"/>
@@ -6181,7 +6816,7 @@
       <x:c r="Y213" s="1"/>
       <x:c r="Z213" s="1"/>
     </x:row>
-    <x:row r="214" ht="18" customHeight="1">
+    <x:row r="214" spans="1:26" ht="18" customHeight="1">
       <x:c r="A214" s="5"/>
       <x:c r="B214" s="5"/>
       <x:c r="C214" s="5"/>
@@ -6209,7 +6844,7 @@
       <x:c r="Y214" s="1"/>
       <x:c r="Z214" s="1"/>
     </x:row>
-    <x:row r="215" ht="18" customHeight="1">
+    <x:row r="215" spans="1:26" ht="18" customHeight="1">
       <x:c r="A215" s="5"/>
       <x:c r="B215" s="5"/>
       <x:c r="C215" s="5"/>
@@ -6237,7 +6872,7 @@
       <x:c r="Y215" s="1"/>
       <x:c r="Z215" s="1"/>
     </x:row>
-    <x:row r="216" ht="18" customHeight="1">
+    <x:row r="216" spans="1:26" ht="18" customHeight="1">
       <x:c r="A216" s="5"/>
       <x:c r="B216" s="5"/>
       <x:c r="C216" s="5"/>
@@ -6265,7 +6900,7 @@
       <x:c r="Y216" s="1"/>
       <x:c r="Z216" s="1"/>
     </x:row>
-    <x:row r="217" ht="18" customHeight="1">
+    <x:row r="217" spans="1:26" ht="18" customHeight="1">
       <x:c r="A217" s="5"/>
       <x:c r="B217" s="5"/>
       <x:c r="C217" s="5"/>
@@ -6293,7 +6928,7 @@
       <x:c r="Y217" s="1"/>
       <x:c r="Z217" s="1"/>
     </x:row>
-    <x:row r="218" ht="18" customHeight="1">
+    <x:row r="218" spans="1:26" ht="18" customHeight="1">
       <x:c r="A218" s="5"/>
       <x:c r="B218" s="5"/>
       <x:c r="C218" s="5"/>
@@ -6321,7 +6956,7 @@
       <x:c r="Y218" s="1"/>
       <x:c r="Z218" s="1"/>
     </x:row>
-    <x:row r="219" ht="18" customHeight="1">
+    <x:row r="219" spans="1:26" ht="18" customHeight="1">
       <x:c r="A219" s="5"/>
       <x:c r="B219" s="5"/>
       <x:c r="C219" s="5"/>
@@ -6349,7 +6984,7 @@
       <x:c r="Y219" s="1"/>
       <x:c r="Z219" s="1"/>
     </x:row>
-    <x:row r="220" ht="18" customHeight="1">
+    <x:row r="220" spans="1:26" ht="18" customHeight="1">
       <x:c r="A220" s="5"/>
       <x:c r="B220" s="5"/>
       <x:c r="C220" s="5"/>
@@ -6377,7 +7012,7 @@
       <x:c r="Y220" s="1"/>
       <x:c r="Z220" s="1"/>
     </x:row>
-    <x:row r="221" ht="18" customHeight="1">
+    <x:row r="221" spans="1:26" ht="18" customHeight="1">
       <x:c r="A221" s="1"/>
       <x:c r="B221" s="1"/>
       <x:c r="C221" s="1"/>
@@ -6405,7 +7040,7 @@
       <x:c r="Y221" s="1"/>
       <x:c r="Z221" s="1"/>
     </x:row>
-    <x:row r="222" ht="18" customHeight="1">
+    <x:row r="222" spans="1:26" ht="18" customHeight="1">
       <x:c r="A222" s="1"/>
       <x:c r="B222" s="1"/>
       <x:c r="C222" s="1"/>
@@ -6433,7 +7068,7 @@
       <x:c r="Y222" s="1"/>
       <x:c r="Z222" s="1"/>
     </x:row>
-    <x:row r="223" ht="18" customHeight="1">
+    <x:row r="223" spans="1:26" ht="18" customHeight="1">
       <x:c r="A223" s="1"/>
       <x:c r="B223" s="1"/>
       <x:c r="C223" s="1"/>
@@ -6461,7 +7096,7 @@
       <x:c r="Y223" s="1"/>
       <x:c r="Z223" s="1"/>
     </x:row>
-    <x:row r="224" ht="18" customHeight="1">
+    <x:row r="224" spans="1:26" ht="18" customHeight="1">
       <x:c r="A224" s="1"/>
       <x:c r="B224" s="1"/>
       <x:c r="C224" s="1"/>
@@ -6489,7 +7124,7 @@
       <x:c r="Y224" s="1"/>
       <x:c r="Z224" s="1"/>
     </x:row>
-    <x:row r="225" ht="18" customHeight="1">
+    <x:row r="225" spans="1:26" ht="18" customHeight="1">
       <x:c r="A225" s="1"/>
       <x:c r="B225" s="1"/>
       <x:c r="C225" s="1"/>
@@ -7269,7 +7904,7 @@
     <x:row r="975" ht="15.75" customHeight="1"/>
     <x:row r="976" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells>
+  <x:mergeCells count="18">
     <x:mergeCell ref="B5:B9"/>
     <x:mergeCell ref="C23:C24"/>
     <x:mergeCell ref="A1:G1"/>
@@ -7289,6 +7924,7 @@
     <x:mergeCell ref="C26:C27"/>
     <x:mergeCell ref="B13:B20"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/docs/한재웅/요구사항정의서_v8.xlsx
+++ b/docs/한재웅/요구사항정의서_v8.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22836" windowHeight="8712" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,63 +19,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <x:si>
     <x:t>시스템은 마이페이지 메인화면의 리포트 보관함 아티팩트 또는 버튼을 통해 마음리포트 보관함 페이지로 이동할 수 있도록 해야 한다. 보관함 진입 후의 주간·월간 캘린더, 일별 대표 감정 이모지, 리포트 상세 조회, 발급 기준 및 공유 기능은 마음리포트 모듈의 정책을 따른다. 마이페이지는 진입 동선, 빈 상태 안내, 리포트 생성 유도 문구, 목록 조회 실패 시 오류 메시지와 재시도 기능을 제공해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 마이페이지 진입 시 정적 아이소메트릭 방 일러스트를 웹 화면의 메인 메뉴 배경으로 표시해야 한다. 방 내부의 프로필, 리포트 보관함, 개인 분석(MBTI 성향 분석, 취향 및 선호 경향 분석), 설정 등 주요 아티팩트는 이미지 위에 클릭 가능한 버튼 또는 링크 영역으로 배치해야 한다. 사용자가 마우스 클릭, 키보드 선택, 포커스 이동으로 아티팩트를 선택하면 호버·포커스·선택 피드백을 제공한 뒤 해당 페이지로 이동해야 하며, 작은 화면에서는 동일 기능을 목록 또는 그리드 메뉴로 함께 제공해야 한다. 로딩 실패 시에는 오류 메시지와 재시도 안내를 표시해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화기록 기반 취향 및 선호 경향 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 사용자가 온보딩에서 입력한 이름, 캐릭터, MBTI, 성별, 나이, 현재 나의 상태, 나를 표현하는 키워드, 관심 분야, 취미 등 기본 프로필 정보를 항목별로 조회할 수 있도록 해야 한다. 수정 가능한 항목은 온보딩 입력 항목과 충돌하지 않도록 동일한 데이터 기준을 사용하며, 수정 완료 시 변경된 정보가 마이페이지 표시와 대화 개인화 설정에 즉시 반영되어야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 사용자의 대화기록에서 반복적으로 나타나는 관심 주제, 선호 표현, 감정 반응, 콘텐츠 취향을 분석해야 한다. 분석 결과는 '최근 관심사', '선호 경향', '변화 추이'로 구분해 제공하며, 데이터가 부족하거나 분석 기준을 충족하지 못한 경우에는 분석 불가 사유와 다음 갱신 가능 조건을 안내해야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템은 사용자의 일반 자유형 대화기록을 분석 파이프라인을 통해 분석하여 대화에서 드러나는 최근의 MBTI 유사 성향과 변화 경향을 추정해야 한다. 분석 결과는 자기이해를 돕는 참고 정보로 제공하며, 추정 근거 리포트와 MBTI 축별 추정 점수 방사형 그래프로 표현하여 한눈에 볼 수 있어야 한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인화면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마이페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요구사항명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>추가설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필 조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>온보딩 사용자 정보 연계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음리포트 담당 범위와 연결</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정적 이미지+클릭 영역 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인 분석 화면 자체 처리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화기록 기반 MBTI 성향 추정 및 경향 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비의료 참고 정보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리포트 보관함 연결</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MY-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소분류(기능설명)</x:t>
   </x:si>
   <x:si>
     <x:t>요구사항 정의서</x:t>
   </x:si>
   <x:si>
-    <x:t>소분류(기능설명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템은 사용자의 대화기록에서 반복적으로 나타나는 관심 주제, 선호 표현, 감정 반응, 콘텐츠 취향을 분석해야 한다. 분석 결과는 '최근 관심사', '선호 경향', '변화 추이'로 구분해 제공하며, 데이터가 부족하거나 분석 기준을 충족하지 못한 경우에는 분석 불가 사유와 다음 갱신 가능 조건을 안내해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계정 탈퇴·데이터 삭제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정적 방 일러스트 기반 메인 메뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자가 설정 페이지의 값을 변경하면 페이지 새로고침 없이 즉시 화면과 관련 공통 UI에 반영되어야 한다. 시스템은 변경 성공 시 확인 토스트를 표시하고, 저장 실패·네트워크 오류·권한 오류 발생 시 원인과 재시도 방법을 안내해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자는 언어, 테마, 접근성, 화면 표시 방식 등 설정 페이지에서 관리하는 개인 설정값을 기본값으로 초기화할 수 있어야 한다. 초기화 전 변경 대상과 복구 가능 여부를 안내하고, 초기화 완료 후 즉시 현재 화면에 반영해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템은 마이페이지 진입 시 정적 아이소메트릭 방 일러스트를 웹 화면의 메인 메뉴 배경으로 표시해야 한다. 방 내부의 프로필, 리포트 보관함, 개인 분석(MBTI 성향 분석, 취향 및 선호 경향 분석), 설정 등 주요 아티팩트는 이미지 위에 클릭 가능한 버튼 또는 링크 영역으로 배치해야 한다. 사용자가 마우스 클릭, 키보드 선택, 포커스 이동으로 아티팩트를 선택하면 호버·포커스·선택 피드백을 제공한 뒤 해당 페이지로 이동해야 하며, 작은 화면에서는 동일 기능을 목록 또는 그리드 메뉴로 함께 제공해야 한다. 로딩 실패 시에는 오류 메시지와 재시도 안내를 표시해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자는 현재 로그인된 브라우저 세션과 최근 접속 이력을 확인하고, 더 이상 사용하지 않는 세션을 종료할 수 있어야 한다. 세션 종료 시 해당 브라우저에서는 재로그인 전까지 서비스 접근이 제한되며, 현재 사용 중인 세션 종료 여부는 별도 확인 절차를 거쳐야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템은 사용자의 일반 자유형 대화기록을 분석 파이프라인을 통해 분석하여 대화에서 드러나는 최근의 MBTI 유사 성향과 변화 경향을 추정해야 한다. 분석 결과는 자기이해를 돕는 참고 정보로 제공하며, 추정 근거 리포트와 MBTI 축별 추정 점수 방사형 그래프로 표현하여 한눈에 볼 수 있어야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자는 설정 화면에서 로그인 계정, 닉네임, 가입 방식, 가입일 등 계정의 기본 정보를 확인할 수 있어야 한다. 이 화면은 다른 기능의 입력값을 직접 수정하지 않고, 상세 수정이 필요한 경우 해당 기능 화면으로 이동할 수 있는 안내만 제공해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자는 설정 화면에서 글자 크기, 애니메이션 최소화, 고대비 표시 등 화면 접근성 옵션을 변경할 수 있어야 한다. 변경된 옵션은 설정 페이지와 공통 UI 컴포넌트에 적용되며, 사용자가 언제든 기본값으로 되돌릴 수 있어야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자는 인터페이스 언어를 한국어 또는 영어로 선택할 수 있고, 화면 테마를 다크 모드 또는 라이트 모드로 변경할 수 있어야 한다. 변경된 언어와 테마는 로그인 계정 기준으로 저장되어 동일 브라우저 재방문 또는 다른 브라우저 로그인 후에도 유지되어야 하며, 접근성 기준을 고려해 텍스트 대비와 주요 버튼 가독성을 보장해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화기록 기반 취향 및 선호 경향 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화기록 기반 MBTI 성향 추정 및 경향 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분류</x:t>
+    <x:t>기능</x:t>
   </x:si>
   <x:si>
     <x:t>비고</x:t>
   </x:si>
   <x:si>
-    <x:t>조회</x:t>
+    <x:t>분류</x:t>
   </x:si>
   <x:si>
     <x:t>대분류</x:t>
@@ -84,139 +117,10 @@
     <x:t>중분류</x:t>
   </x:si>
   <x:si>
-    <x:t>기능</x:t>
+    <x:t>조회</x:t>
   </x:si>
   <x:si>
-    <x:t>설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비기능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자가 계정 탈퇴를 요청하면 시스템은 탈퇴 전 삭제 대상 데이터 범위와 복구 불가 여부를 안내해야 한다. 최종 확인 후 대화기록, 결과카드, 메모리, 개인화 설정, 웹 설정값 등 계정에 연결된 데이터를 삭제 처리하고, 삭제 완료 화면 및 필요 시 이메일 확인 안내를 제공해야 한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-MY-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-MY-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리포트 보관함 연결</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-MY-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-MY-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비의료 참고 정보</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정 내 계정 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-MY-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-SET-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계정 기본 정보 조회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정 자체 제공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 접근성 설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-SET-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-SET-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-SET-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어·테마 설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전역 UI 설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로그인 세션 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정 데이터 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개인정보보호 정책</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-SET-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F-SET-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웹 계정 보안 설정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NF-SET-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정 즉시 반영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>추가설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로필 조회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요구사항명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정책·제약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개인 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마이페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메인화면</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정 페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요구사항 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설정값 초기화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UX 일관성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>온보딩 사용자 정보 연계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정적 이미지+클릭 영역 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개인 분석 화면 자체 처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마음리포트 담당 범위와 연결</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템은 사용자가 온보딩에서 입력한 이름, 캐릭터, MBTI, 성별, 나이, 현재 나의 상태, 나를 표현하는 키워드, 관심 분야, 취미 등 기본 프로필 정보를 항목별로 조회할 수 있도록 해야 한다. 수정 가능한 항목은 온보딩 입력 항목과 충돌하지 않도록 동일한 데이터 기준을 사용하며, 수정 완료 시 변경된 정보가 마이페이지 표시와 대화 개인화 설정에 즉시 반영되어야 한다.</x:t>
+    <x:t>정적 방 일러스트 기반 메인 메뉴</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -263,7 +167,7 @@
       <x:patternFill patternType="gray125"/>
     </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="7">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -327,10 +231,10 @@
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
-      <x:top style="dotted">
+      <x:top>
         <x:color auto="1"/>
       </x:top>
-      <x:bottom style="dotted">
+      <x:bottom>
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
@@ -341,21 +245,7 @@
       <x:right style="thin">
         <x:color auto="1"/>
       </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left>
-        <x:color auto="1"/>
-      </x:left>
-      <x:right>
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
+      <x:top style="dotted">
         <x:color auto="1"/>
       </x:top>
       <x:bottom style="dotted">
@@ -364,20 +254,6 @@
     </x:border>
     <x:border>
       <x:left>
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="dotted">
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
         <x:color auto="1"/>
       </x:left>
       <x:right style="thin">
@@ -402,7 +278,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -427,41 +303,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
@@ -469,13 +315,34 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1019,21 +886,21 @@
   <x:dimension ref="A1:Z225"/>
   <x:sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="14.199999999999999"/>
   <x:cols>
-    <x:col min="5" max="5" width="56.63671875" style="16" customWidth="1"/>
+    <x:col min="5" max="5" width="56.63671875" style="9" customWidth="1"/>
     <x:col min="6" max="6" width="56" style="7" customWidth="1"/>
-    <x:col min="7" max="7" width="26.76953125" style="16" customWidth="1"/>
+    <x:col min="7" max="7" width="26.76953125" style="9" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:26" ht="18" customHeight="1">
-      <x:c r="A1" s="21" t="s">
-        <x:v>1</x:v>
+      <x:c r="A1" s="11" t="s">
+        <x:v>26</x:v>
       </x:c>
-      <x:c r="B1" s="21"/>
-      <x:c r="C1" s="21"/>
-      <x:c r="D1" s="21"/>
-      <x:c r="E1" s="21"/>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="21"/>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+      <x:c r="F1" s="11"/>
+      <x:c r="G1" s="11"/>
       <x:c r="H1" s="1"/>
       <x:c r="I1" s="1"/>
       <x:c r="J1" s="1"/>
@@ -1083,20 +950,20 @@
       <x:c r="Z2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:26" ht="36" customHeight="1">
-      <x:c r="A3" s="20" t="s">
-        <x:v>16</x:v>
+      <x:c r="A3" s="10" t="s">
+        <x:v>29</x:v>
       </x:c>
-      <x:c r="B3" s="20" t="s">
-        <x:v>52</x:v>
+      <x:c r="B3" s="10" t="s">
+        <x:v>9</x:v>
       </x:c>
-      <x:c r="C3" s="20"/>
-      <x:c r="D3" s="20"/>
-      <x:c r="E3" s="20"/>
-      <x:c r="F3" s="20" t="s">
-        <x:v>50</x:v>
+      <x:c r="C3" s="10"/>
+      <x:c r="D3" s="10"/>
+      <x:c r="E3" s="10"/>
+      <x:c r="F3" s="10" t="s">
+        <x:v>10</x:v>
       </x:c>
-      <x:c r="G3" s="20" t="s">
-        <x:v>17</x:v>
+      <x:c r="G3" s="10" t="s">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
       <x:c r="I3" s="1"/>
@@ -1119,21 +986,21 @@
       <x:c r="Z3" s="1"/>
     </x:row>
     <x:row r="4" spans="1:26" ht="18" customHeight="1">
-      <x:c r="A4" s="20"/>
-      <x:c r="B4" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="A4" s="10"/>
+      <x:c r="B4" s="8" t="s">
+        <x:v>30</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="C4" s="8" t="s">
+        <x:v>31</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="s">
-        <x:v>58</x:v>
+      <x:c r="D4" s="8" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>25</x:v>
       </x:c>
-      <x:c r="F4" s="20"/>
-      <x:c r="G4" s="20"/>
+      <x:c r="F4" s="10"/>
+      <x:c r="G4" s="10"/>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
       <x:c r="J4" s="1"/>
@@ -1155,26 +1022,26 @@
       <x:c r="Z4" s="1"/>
     </x:row>
     <x:row r="5" spans="1:26" ht="96" customHeight="1">
-      <x:c r="A5" s="19" t="s">
+      <x:c r="A5" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B5" s="19" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="19" t="s">
-        <x:v>55</x:v>
+      <x:c r="E5" s="12" t="s">
+        <x:v>33</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="s">
-        <x:v>56</x:v>
+      <x:c r="F5" s="14" t="s">
+        <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G5" s="8" t="s">
-        <x:v>62</x:v>
+      <x:c r="G5" s="15" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
       <x:c r="I5" s="1"/>
@@ -1197,22 +1064,22 @@
       <x:c r="Z5" s="1"/>
     </x:row>
     <x:row r="6" spans="1:26" ht="72" customHeight="1">
-      <x:c r="A6" s="19"/>
+      <x:c r="A6" s="16"/>
       <x:c r="B6" s="19"/>
-      <x:c r="C6" s="22" t="s">
-        <x:v>18</x:v>
+      <x:c r="C6" s="20" t="s">
+        <x:v>32</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="s">
-        <x:v>25</x:v>
+      <x:c r="D6" s="12" t="s">
+        <x:v>24</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="s">
-        <x:v>51</x:v>
+      <x:c r="E6" s="12" t="s">
+        <x:v>12</x:v>
       </x:c>
-      <x:c r="F6" s="17" t="s">
-        <x:v>65</x:v>
+      <x:c r="F6" s="14" t="s">
+        <x:v>3</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="s">
-        <x:v>61</x:v>
+      <x:c r="G6" s="15" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
       <x:c r="I6" s="1"/>
@@ -1235,20 +1102,20 @@
       <x:c r="Z6" s="1"/>
     </x:row>
     <x:row r="7" spans="1:26" ht="72" customHeight="1">
-      <x:c r="A7" s="19"/>
+      <x:c r="A7" s="16"/>
       <x:c r="B7" s="19"/>
-      <x:c r="C7" s="23"/>
-      <x:c r="D7" s="14" t="s">
-        <x:v>28</x:v>
+      <x:c r="C7" s="21"/>
+      <x:c r="D7" s="12" t="s">
+        <x:v>18</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
-        <x:v>27</x:v>
+      <x:c r="E7" s="12" t="s">
+        <x:v>23</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="s">
-        <x:v>64</x:v>
+      <x:c r="G7" s="15" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="1"/>
       <x:c r="I7" s="1"/>
@@ -1271,22 +1138,22 @@
       <x:c r="Z7" s="1"/>
     </x:row>
     <x:row r="8" spans="1:26" ht="60" customHeight="1">
-      <x:c r="A8" s="19"/>
+      <x:c r="A8" s="16"/>
       <x:c r="B8" s="19"/>
-      <x:c r="C8" s="22" t="s">
-        <x:v>54</x:v>
+      <x:c r="C8" s="20" t="s">
+        <x:v>11</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>29</x:v>
+      <x:c r="D8" s="12" t="s">
+        <x:v>22</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>15</x:v>
+      <x:c r="E8" s="12" t="s">
+        <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="17" t="s">
-        <x:v>10</x:v>
+      <x:c r="F8" s="14" t="s">
+        <x:v>5</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>30</x:v>
+      <x:c r="G8" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="1"/>
       <x:c r="I8" s="1"/>
@@ -1309,20 +1176,20 @@
       <x:c r="Z8" s="1"/>
     </x:row>
     <x:row r="9" spans="1:26" ht="72" customHeight="1">
-      <x:c r="A9" s="19"/>
+      <x:c r="A9" s="16"/>
       <x:c r="B9" s="19"/>
-      <x:c r="C9" s="23"/>
-      <x:c r="D9" s="14" t="s">
-        <x:v>32</x:v>
+      <x:c r="C9" s="21"/>
+      <x:c r="D9" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>14</x:v>
+      <x:c r="E9" s="12" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="F9" s="17" t="s">
-        <x:v>3</x:v>
+      <x:c r="F9" s="14" t="s">
+        <x:v>4</x:v>
       </x:c>
-      <x:c r="G9" s="8" t="s">
-        <x:v>63</x:v>
+      <x:c r="G9" s="18" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1"/>
       <x:c r="I9" s="1"/>
@@ -1345,25 +1212,13 @@
       <x:c r="Z9" s="1"/>
     </x:row>
     <x:row r="10" spans="1:26" ht="72" customHeight="1">
-      <x:c r="A10" s="19"/>
-      <x:c r="B10" s="20" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G10" s="8" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="A10" s="14"/>
+      <x:c r="B10" s="12"/>
+      <x:c r="C10" s="14"/>
+      <x:c r="D10" s="12"/>
+      <x:c r="E10" s="12"/>
+      <x:c r="F10" s="14"/>
+      <x:c r="G10" s="17"/>
       <x:c r="H10" s="1"/>
       <x:c r="I10" s="1"/>
       <x:c r="J10" s="1"/>
@@ -1385,21 +1240,13 @@
       <x:c r="Z10" s="1"/>
     </x:row>
     <x:row r="11" spans="1:26" ht="60" customHeight="1">
-      <x:c r="A11" s="19"/>
-      <x:c r="B11" s="20"/>
-      <x:c r="C11" s="23"/>
-      <x:c r="D11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G11" s="8" t="s">
-        <x:v>41</x:v>
-      </x:c>
+      <x:c r="A11" s="14"/>
+      <x:c r="B11" s="12"/>
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="12"/>
+      <x:c r="E11" s="12"/>
+      <x:c r="F11" s="14"/>
+      <x:c r="G11" s="17"/>
       <x:c r="H11" s="1"/>
       <x:c r="I11" s="1"/>
       <x:c r="J11" s="1"/>
@@ -1421,201 +1268,157 @@
       <x:c r="Z11" s="1"/>
     </x:row>
     <x:row r="12" spans="1:7" ht="72" customHeight="1">
-      <x:c r="A12" s="19"/>
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="18"/>
-      <x:c r="D12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G12" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
+      <x:c r="A12" s="14"/>
+      <x:c r="B12" s="12"/>
+      <x:c r="C12" s="12"/>
+      <x:c r="D12" s="12"/>
+      <x:c r="E12" s="12"/>
+      <x:c r="F12" s="14"/>
+      <x:c r="G12" s="17"/>
     </x:row>
     <x:row r="13" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A13" s="19"/>
-      <x:c r="B13" s="20"/>
-      <x:c r="C13" s="24"/>
-      <x:c r="D13" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G13" s="8" t="s">
-        <x:v>47</x:v>
-      </x:c>
+      <x:c r="A13" s="14"/>
+      <x:c r="B13" s="12"/>
+      <x:c r="C13" s="12"/>
+      <x:c r="D13" s="12"/>
+      <x:c r="E13" s="12"/>
+      <x:c r="F13" s="14"/>
+      <x:c r="G13" s="17"/>
     </x:row>
     <x:row r="14" spans="1:7" ht="72" customHeight="1">
-      <x:c r="A14" s="19"/>
-      <x:c r="B14" s="20"/>
-      <x:c r="C14" s="23"/>
-      <x:c r="D14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G14" s="8" t="s">
-        <x:v>43</x:v>
-      </x:c>
+      <x:c r="A14" s="14"/>
+      <x:c r="B14" s="12"/>
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="12"/>
+      <x:c r="E14" s="12"/>
+      <x:c r="F14" s="14"/>
+      <x:c r="G14" s="17"/>
     </x:row>
     <x:row r="15" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A15" s="19"/>
-      <x:c r="B15" s="20"/>
-      <x:c r="C15" s="23"/>
-      <x:c r="D15" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G15" s="8" t="s">
-        <x:v>44</x:v>
-      </x:c>
+      <x:c r="A15" s="14"/>
+      <x:c r="B15" s="12"/>
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12"/>
+      <x:c r="E15" s="12"/>
+      <x:c r="F15" s="14"/>
+      <x:c r="G15" s="17"/>
     </x:row>
     <x:row r="16" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A16" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B16" s="20"/>
-      <x:c r="C16" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D16" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G16" s="8" t="s">
-        <x:v>60</x:v>
-      </x:c>
+      <x:c r="A16" s="14"/>
+      <x:c r="B16" s="12"/>
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12"/>
+      <x:c r="E16" s="12"/>
+      <x:c r="F16" s="14"/>
+      <x:c r="G16" s="17"/>
     </x:row>
     <x:row r="17" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A17" s="19"/>
-      <x:c r="B17" s="20"/>
-      <x:c r="C17" s="23"/>
-      <x:c r="D17" s="14"/>
-      <x:c r="E17" s="14"/>
-      <x:c r="F17" s="17"/>
-      <x:c r="G17" s="8"/>
+      <x:c r="A17" s="14"/>
+      <x:c r="B17" s="12"/>
+      <x:c r="C17" s="12"/>
+      <x:c r="D17" s="12"/>
+      <x:c r="E17" s="12"/>
+      <x:c r="F17" s="14"/>
+      <x:c r="G17" s="17"/>
     </x:row>
     <x:row r="18" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A18" s="19"/>
-      <x:c r="B18" s="20"/>
-      <x:c r="C18" s="23"/>
-      <x:c r="D18" s="14"/>
-      <x:c r="E18" s="14"/>
-      <x:c r="F18" s="17"/>
-      <x:c r="G18" s="8"/>
+      <x:c r="A18" s="14"/>
+      <x:c r="B18" s="12"/>
+      <x:c r="C18" s="12"/>
+      <x:c r="D18" s="12"/>
+      <x:c r="E18" s="12"/>
+      <x:c r="F18" s="14"/>
+      <x:c r="G18" s="17"/>
     </x:row>
     <x:row r="19" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A19" s="19"/>
-      <x:c r="B19" s="20"/>
-      <x:c r="C19" s="23"/>
-      <x:c r="D19" s="14"/>
-      <x:c r="E19" s="14"/>
-      <x:c r="F19" s="17"/>
-      <x:c r="G19" s="8"/>
+      <x:c r="A19" s="14"/>
+      <x:c r="B19" s="12"/>
+      <x:c r="C19" s="12"/>
+      <x:c r="D19" s="12"/>
+      <x:c r="E19" s="12"/>
+      <x:c r="F19" s="14"/>
+      <x:c r="G19" s="17"/>
     </x:row>
     <x:row r="20" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A20" s="14"/>
-      <x:c r="B20" s="20"/>
-      <x:c r="C20" s="14"/>
-      <x:c r="D20" s="14"/>
-      <x:c r="E20" s="8"/>
-      <x:c r="F20" s="9"/>
-      <x:c r="G20" s="10"/>
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="12"/>
+      <x:c r="C20" s="12"/>
+      <x:c r="D20" s="12"/>
+      <x:c r="E20" s="12"/>
+      <x:c r="F20" s="14"/>
+      <x:c r="G20" s="17"/>
     </x:row>
     <x:row r="21" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A21" s="20"/>
-      <x:c r="B21" s="20"/>
-      <x:c r="C21" s="20"/>
-      <x:c r="D21" s="11"/>
+      <x:c r="A21" s="10"/>
+      <x:c r="B21" s="12"/>
+      <x:c r="C21" s="12"/>
+      <x:c r="D21" s="12"/>
       <x:c r="E21" s="12"/>
-      <x:c r="F21" s="13"/>
-      <x:c r="G21" s="12"/>
+      <x:c r="F21" s="14"/>
+      <x:c r="G21" s="17"/>
     </x:row>
     <x:row r="22" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A22" s="20"/>
-      <x:c r="B22" s="20"/>
-      <x:c r="C22" s="20"/>
-      <x:c r="D22" s="11"/>
+      <x:c r="A22" s="10"/>
+      <x:c r="B22" s="12"/>
+      <x:c r="C22" s="12"/>
+      <x:c r="D22" s="12"/>
       <x:c r="E22" s="12"/>
-      <x:c r="F22" s="13"/>
-      <x:c r="G22" s="12"/>
+      <x:c r="F22" s="14"/>
+      <x:c r="G22" s="17"/>
     </x:row>
     <x:row r="23" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A23" s="20"/>
-      <x:c r="B23" s="20"/>
-      <x:c r="C23" s="20"/>
-      <x:c r="D23" s="11"/>
+      <x:c r="A23" s="10"/>
+      <x:c r="B23" s="12"/>
+      <x:c r="C23" s="12"/>
+      <x:c r="D23" s="12"/>
       <x:c r="E23" s="12"/>
-      <x:c r="F23" s="13"/>
-      <x:c r="G23" s="12"/>
+      <x:c r="F23" s="14"/>
+      <x:c r="G23" s="17"/>
     </x:row>
     <x:row r="24" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A24" s="20"/>
-      <x:c r="B24" s="20"/>
-      <x:c r="C24" s="20"/>
-      <x:c r="D24" s="11"/>
+      <x:c r="A24" s="10"/>
+      <x:c r="B24" s="12"/>
+      <x:c r="C24" s="12"/>
+      <x:c r="D24" s="12"/>
       <x:c r="E24" s="12"/>
-      <x:c r="F24" s="13"/>
-      <x:c r="G24" s="12"/>
+      <x:c r="F24" s="14"/>
+      <x:c r="G24" s="17"/>
     </x:row>
     <x:row r="25" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A25" s="20"/>
-      <x:c r="B25" s="20"/>
-      <x:c r="C25" s="14"/>
-      <x:c r="D25" s="11"/>
+      <x:c r="A25" s="10"/>
+      <x:c r="B25" s="12"/>
+      <x:c r="C25" s="12"/>
+      <x:c r="D25" s="12"/>
       <x:c r="E25" s="12"/>
-      <x:c r="F25" s="13"/>
-      <x:c r="G25" s="12"/>
+      <x:c r="F25" s="14"/>
+      <x:c r="G25" s="17"/>
     </x:row>
     <x:row r="26" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A26" s="20"/>
-      <x:c r="B26" s="20"/>
-      <x:c r="C26" s="20"/>
-      <x:c r="D26" s="11"/>
+      <x:c r="A26" s="10"/>
+      <x:c r="B26" s="12"/>
+      <x:c r="C26" s="12"/>
+      <x:c r="D26" s="12"/>
       <x:c r="E26" s="12"/>
-      <x:c r="F26" s="13"/>
-      <x:c r="G26" s="12"/>
+      <x:c r="F26" s="14"/>
+      <x:c r="G26" s="17"/>
     </x:row>
     <x:row r="27" spans="1:7" ht="60" customHeight="1">
-      <x:c r="A27" s="20"/>
-      <x:c r="B27" s="20"/>
-      <x:c r="C27" s="20"/>
-      <x:c r="D27" s="11"/>
+      <x:c r="A27" s="10"/>
+      <x:c r="B27" s="12"/>
+      <x:c r="C27" s="12"/>
+      <x:c r="D27" s="12"/>
       <x:c r="E27" s="12"/>
-      <x:c r="F27" s="13"/>
-      <x:c r="G27" s="12"/>
+      <x:c r="F27" s="14"/>
+      <x:c r="G27" s="17"/>
     </x:row>
     <x:row r="28" spans="1:26" ht="60" customHeight="1">
-      <x:c r="A28" s="20"/>
-      <x:c r="B28" s="20"/>
-      <x:c r="C28" s="14"/>
-      <x:c r="D28" s="11"/>
+      <x:c r="A28" s="10"/>
+      <x:c r="B28" s="12"/>
+      <x:c r="C28" s="12"/>
+      <x:c r="D28" s="12"/>
       <x:c r="E28" s="12"/>
       <x:c r="F28" s="12"/>
-      <x:c r="G28" s="12"/>
+      <x:c r="G28" s="17"/>
       <x:c r="H28" s="4"/>
       <x:c r="I28" s="1"/>
       <x:c r="J28" s="1"/>
@@ -7904,27 +7707,19 @@
     <x:row r="975" ht="15.75" customHeight="1"/>
     <x:row r="976" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="18">
-    <x:mergeCell ref="B5:B9"/>
-    <x:mergeCell ref="C23:C24"/>
+  <x:mergeCells count="10">
     <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="C8:C9"/>
-    <x:mergeCell ref="B10:B12"/>
     <x:mergeCell ref="A3:A4"/>
     <x:mergeCell ref="G3:G4"/>
     <x:mergeCell ref="A21:A28"/>
-    <x:mergeCell ref="C13:C19"/>
-    <x:mergeCell ref="B21:B28"/>
     <x:mergeCell ref="F3:F4"/>
-    <x:mergeCell ref="C21:C22"/>
-    <x:mergeCell ref="C10:C11"/>
     <x:mergeCell ref="B3:E3"/>
+    <x:mergeCell ref="A5:A9"/>
+    <x:mergeCell ref="B5:B9"/>
     <x:mergeCell ref="C6:C7"/>
-    <x:mergeCell ref="A5:A19"/>
-    <x:mergeCell ref="C26:C27"/>
-    <x:mergeCell ref="B13:B20"/>
+    <x:mergeCell ref="C8:C9"/>
   </x:mergeCells>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>